--- a/LEVI.xlsx
+++ b/LEVI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6AE105-E4F1-4AE6-90DC-1882E6CCBF42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39DC7321-BB3D-4D60-B837-A0828AA37A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{D6D5C0B0-0DA9-4C26-A53F-ED546E3BB507}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{D6D5C0B0-0DA9-4C26-A53F-ED546E3BB507}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="71">
   <si>
     <t>Levis &amp; Strauss</t>
   </si>
@@ -257,6 +257,18 @@
   <si>
     <t>FY25</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -266,13 +278,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -460,37 +478,41 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -868,7 +890,7 @@
         <v>3</v>
       </c>
       <c r="I2" s="3">
-        <v>21.96</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -876,11 +898,11 @@
         <v>4</v>
       </c>
       <c r="I3" s="3">
-        <f>103.742231+286.725056</f>
-        <v>390.467287</v>
-      </c>
-      <c r="J3" s="23" t="s">
-        <v>58</v>
+        <f>98.176901+286.41935</f>
+        <v>384.596251</v>
+      </c>
+      <c r="J3" s="25" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -893,7 +915,7 @@
       </c>
       <c r="I4" s="3">
         <f>I3*I2</f>
-        <v>8574.6616225199996</v>
+        <v>8753.410672760001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -904,11 +926,11 @@
         <v>6</v>
       </c>
       <c r="I5" s="3">
-        <f>757.9+90.9</f>
-        <v>848.8</v>
-      </c>
-      <c r="J5" s="23" t="s">
-        <v>58</v>
+        <f>716.6+95.4</f>
+        <v>812</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -916,10 +938,10 @@
         <v>7</v>
       </c>
       <c r="I6" s="3">
-        <v>1039.2</v>
-      </c>
-      <c r="J6" s="23" t="s">
-        <v>58</v>
+        <v>1049.4000000000001</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -934,7 +956,7 @@
       </c>
       <c r="I7" s="3">
         <f>I4-I5+I6</f>
-        <v>8765.0616225199992</v>
+        <v>8990.8106727600007</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -990,7 +1012,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24653C7A-501A-410A-9E04-3084EFB9A76F}">
-  <dimension ref="A1:AG330"/>
+  <dimension ref="A1:AK330"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -998,12 +1020,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C2" s="4" t="s">
         <v>11</v>
       </c>
@@ -1040,33 +1062,45 @@
       <c r="N2" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4" t="s">
+      <c r="O2" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="P2" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q2" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="R2" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="U2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="V2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="W2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="X2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="Y2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="Z2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="W2" s="23" t="s">
+      <c r="AA2" s="23" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
         <v>63</v>
@@ -1095,7 +1129,9 @@
         <v>806.4</v>
       </c>
       <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
+      <c r="O3" s="3">
+        <v>855.7</v>
+      </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
@@ -1103,21 +1139,25 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
       <c r="V3" s="3"/>
-      <c r="W3" s="3">
-        <v>3297</v>
-      </c>
+      <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
+      <c r="AA3" s="3">
+        <v>3297</v>
+      </c>
       <c r="AB3" s="3"/>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
       <c r="AE3" s="3"/>
       <c r="AF3" s="3"/>
       <c r="AG3" s="3"/>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="3"/>
+      <c r="AK3" s="3"/>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
       <c r="B4" s="2" t="s">
         <v>64</v>
@@ -1146,7 +1186,9 @@
         <v>426.3</v>
       </c>
       <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
+      <c r="O4" s="3">
+        <v>496</v>
+      </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
@@ -1154,21 +1196,25 @@
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
-      <c r="W4" s="3">
-        <v>1699.3</v>
-      </c>
+      <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
+      <c r="AA4" s="3">
+        <v>1699.3</v>
+      </c>
       <c r="AB4" s="3"/>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
       <c r="AG4" s="3"/>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="3"/>
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3"/>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="2" t="s">
         <v>65</v>
@@ -1197,7 +1243,9 @@
         <v>277.7</v>
       </c>
       <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
+      <c r="O5" s="3">
+        <v>347.5</v>
+      </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -1205,21 +1253,25 @@
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
-      <c r="W5" s="3">
-        <v>1134.4000000000001</v>
-      </c>
+      <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
+      <c r="AA5" s="3">
+        <v>1134.4000000000001</v>
+      </c>
       <c r="AB5" s="3"/>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH5" s="3"/>
+      <c r="AI5" s="3"/>
+      <c r="AJ5" s="3"/>
+      <c r="AK5" s="3"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
       <c r="B6" s="2" t="s">
         <v>61</v>
@@ -1248,7 +1300,9 @@
         <v>832.2</v>
       </c>
       <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
+      <c r="O6" s="3">
+        <v>831</v>
+      </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -1256,21 +1310,25 @@
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
-      <c r="W6" s="3">
-        <v>3205.2</v>
-      </c>
+      <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
+      <c r="AA6" s="3">
+        <v>3205.2</v>
+      </c>
       <c r="AB6" s="3"/>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
       <c r="AG6" s="3"/>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="3"/>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3"/>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A7" s="6"/>
       <c r="B7" s="2" t="s">
         <v>62</v>
@@ -1299,7 +1357,9 @@
         <v>711.2</v>
       </c>
       <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
+      <c r="O7" s="3">
+        <v>911.5</v>
+      </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
@@ -1307,21 +1367,25 @@
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
-      <c r="W7" s="3">
-        <v>3076.8</v>
-      </c>
+      <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
+      <c r="AA7" s="3">
+        <v>3076.8</v>
+      </c>
       <c r="AB7" s="3"/>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
       <c r="AG7" s="3"/>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="3"/>
+      <c r="AI7" s="3"/>
+      <c r="AJ7" s="3"/>
+      <c r="AK7" s="3"/>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A8" s="6"/>
       <c r="B8" s="2" t="s">
         <v>46</v>
@@ -1352,7 +1416,9 @@
         <v>1510.4</v>
       </c>
       <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
+      <c r="O8" s="3">
+        <v>1699.2</v>
+      </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
@@ -1360,21 +1426,25 @@
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
-      <c r="W8" s="3">
-        <v>6130.7</v>
-      </c>
+      <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
+      <c r="AA8" s="3">
+        <v>6130.7</v>
+      </c>
       <c r="AB8" s="3"/>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3"/>
+      <c r="AI8" s="3"/>
+      <c r="AJ8" s="3"/>
+      <c r="AK8" s="3"/>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
       <c r="B9" s="2" t="s">
         <v>52</v>
@@ -1403,7 +1473,9 @@
         <v>33</v>
       </c>
       <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
+      <c r="O9" s="3">
+        <v>43.3</v>
+      </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
@@ -1411,21 +1483,25 @@
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
-      <c r="W9" s="3">
-        <v>151.30000000000001</v>
-      </c>
+      <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
+      <c r="AA9" s="3">
+        <v>151.30000000000001</v>
+      </c>
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3"/>
+      <c r="AI9" s="3"/>
+      <c r="AJ9" s="3"/>
+      <c r="AK9" s="3"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
@@ -1439,7 +1515,7 @@
         <v>1511</v>
       </c>
       <c r="F10" s="19">
-        <f>+U10-SUM(C10:E10)</f>
+        <f>+Y10-SUM(C10:E10)</f>
         <v>1642.3000000000002</v>
       </c>
       <c r="G10" s="19">
@@ -1452,7 +1528,7 @@
         <v>1443.1</v>
       </c>
       <c r="J10" s="19">
-        <f>+V10-SUM(G10:I10)</f>
+        <f>+Z10-SUM(G10:I10)</f>
         <v>1995.8000000000002</v>
       </c>
       <c r="K10" s="19">
@@ -1464,44 +1540,53 @@
       <c r="M10" s="19">
         <v>1543.4</v>
       </c>
-      <c r="N10" s="19"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="19">
+      <c r="N10" s="19">
+        <f>+AA10-SUM(K10:M10)</f>
+        <v>1765.7999999999993</v>
+      </c>
+      <c r="O10" s="19">
+        <v>1742.5</v>
+      </c>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="19">
         <v>5575.44</v>
       </c>
-      <c r="Q10" s="19">
+      <c r="U10" s="19">
         <v>5763.0870000000004</v>
       </c>
-      <c r="R10" s="19">
+      <c r="V10" s="19">
         <v>4452.6090000000004</v>
       </c>
-      <c r="S10" s="19">
+      <c r="W10" s="19">
         <v>5763.9</v>
       </c>
-      <c r="T10" s="19">
+      <c r="X10" s="19">
         <v>6168.6</v>
       </c>
-      <c r="U10" s="19">
+      <c r="Y10" s="19">
         <v>6179</v>
       </c>
-      <c r="V10" s="19">
+      <c r="Z10" s="19">
         <v>6355.3</v>
       </c>
-      <c r="W10" s="19">
+      <c r="AA10" s="19">
         <v>6282</v>
       </c>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
       <c r="AG10" s="3"/>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3"/>
+      <c r="AI10" s="3"/>
+      <c r="AJ10" s="3"/>
+      <c r="AK10" s="3"/>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
@@ -1515,7 +1600,7 @@
         <v>671.5</v>
       </c>
       <c r="F11" s="3">
-        <f>+U11-SUM(C11:E11)</f>
+        <f>+Y11-SUM(C11:E11)</f>
         <v>692.60000000000014</v>
       </c>
       <c r="G11" s="3">
@@ -1528,7 +1613,7 @@
         <v>569.20000000000005</v>
       </c>
       <c r="J11" s="3">
-        <f>+V11-SUM(G11:I11)</f>
+        <f>+Z11-SUM(G11:I11)</f>
         <v>792.7</v>
       </c>
       <c r="K11" s="3">
@@ -1540,44 +1625,53 @@
       <c r="M11" s="3">
         <v>591.79999999999995</v>
       </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3">
+      <c r="N11" s="24">
+        <f>+AA11-SUM(K11:M11)</f>
+        <v>692.99999999999977</v>
+      </c>
+      <c r="O11" s="24">
+        <v>664.2</v>
+      </c>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3">
         <v>2577.4650000000001</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="U11" s="3">
         <v>2661.7139999999999</v>
       </c>
-      <c r="R11" s="3">
+      <c r="V11" s="3">
         <v>2099.6849999999999</v>
       </c>
-      <c r="S11" s="3">
+      <c r="W11" s="3">
         <v>2417.1999999999998</v>
       </c>
-      <c r="T11" s="3">
+      <c r="X11" s="3">
         <v>2619.8000000000002</v>
       </c>
-      <c r="U11" s="3">
+      <c r="Y11" s="3">
         <v>2663.3</v>
       </c>
-      <c r="V11" s="3">
+      <c r="Z11" s="3">
         <v>2539.4</v>
       </c>
-      <c r="W11" s="3">
+      <c r="AA11" s="3">
         <v>2404.1999999999998</v>
       </c>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>27</v>
       </c>
@@ -1625,52 +1719,62 @@
         <f>+M10-M11</f>
         <v>951.60000000000014</v>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3">
-        <f t="shared" ref="P12:T12" si="2">P10-P11</f>
+      <c r="N12" s="3">
+        <f>+N10-N11</f>
+        <v>1072.7999999999995</v>
+      </c>
+      <c r="O12" s="3">
+        <f>+O10-O11</f>
+        <v>1078.3</v>
+      </c>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3">
+        <f t="shared" ref="T12:X12" si="2">T10-T11</f>
         <v>2997.9749999999995</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="U12" s="3">
         <f t="shared" si="2"/>
         <v>3101.3730000000005</v>
       </c>
-      <c r="R12" s="3">
+      <c r="V12" s="3">
         <f t="shared" si="2"/>
         <v>2352.9240000000004</v>
       </c>
-      <c r="S12" s="3">
+      <c r="W12" s="3">
         <f t="shared" si="2"/>
         <v>3346.7</v>
       </c>
-      <c r="T12" s="3">
+      <c r="X12" s="3">
         <f t="shared" si="2"/>
         <v>3548.8</v>
       </c>
-      <c r="U12" s="3">
-        <f>U10-U11</f>
+      <c r="Y12" s="3">
+        <f>Y10-Y11</f>
         <v>3515.7</v>
       </c>
-      <c r="V12" s="3">
-        <f>V10-V11</f>
+      <c r="Z12" s="3">
+        <f>Z10-Z11</f>
         <v>3815.9</v>
       </c>
-      <c r="W12" s="3">
-        <f>+W10-W11</f>
+      <c r="AA12" s="3">
+        <f>+AA10-AA11</f>
         <v>3877.8</v>
       </c>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3"/>
       <c r="AF12" s="3"/>
       <c r="AG12" s="3"/>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3"/>
+      <c r="AI12" s="3"/>
+      <c r="AJ12" s="3"/>
+      <c r="AK12" s="3"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
@@ -1684,7 +1788,7 @@
         <v>713</v>
       </c>
       <c r="F13" s="3">
-        <f t="shared" ref="F13:F14" si="3">+U13-SUM(C13:E13)</f>
+        <f t="shared" ref="F13:F14" si="3">+Y13-SUM(C13:E13)</f>
         <v>817.89999999999964</v>
       </c>
       <c r="G13" s="3">
@@ -1697,7 +1801,7 @@
         <v>726.4</v>
       </c>
       <c r="J13" s="3">
-        <f t="shared" ref="J13:J14" si="4">+V13-SUM(G13:I13)</f>
+        <f t="shared" ref="J13:J14" si="4">+Z13-SUM(G13:I13)</f>
         <v>972.69999999999982</v>
       </c>
       <c r="K13" s="3">
@@ -1709,44 +1813,53 @@
       <c r="M13" s="3">
         <v>775.6</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3">
+      <c r="N13" s="24">
+        <f>+AA13-SUM(K13:M13)</f>
+        <v>857.29999999999973</v>
+      </c>
+      <c r="O13" s="24">
+        <v>871.7</v>
+      </c>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3">
         <v>2457.5639999999999</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="U13" s="3">
         <v>2534.6979999999999</v>
       </c>
-      <c r="R13" s="3">
+      <c r="V13" s="3">
         <v>2347.6280000000002</v>
       </c>
-      <c r="S13" s="3">
+      <c r="W13" s="3">
         <v>2660.5</v>
       </c>
-      <c r="T13" s="3">
+      <c r="X13" s="3">
         <v>2890.7</v>
       </c>
-      <c r="U13" s="3">
+      <c r="Y13" s="3">
         <v>3072.2</v>
       </c>
-      <c r="V13" s="3">
+      <c r="Z13" s="3">
         <v>3246.2</v>
       </c>
-      <c r="W13" s="3">
+      <c r="AA13" s="3">
         <v>3173.2</v>
       </c>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3"/>
       <c r="AF13" s="3"/>
       <c r="AG13" s="3"/>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3"/>
+      <c r="AI13" s="3"/>
+      <c r="AJ13" s="3"/>
+      <c r="AK13" s="3"/>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
@@ -1787,46 +1900,55 @@
       <c r="M14" s="3">
         <v>8.6</v>
       </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3">
+      <c r="N14" s="24">
+        <f>+AA14-SUM(K14:M14)</f>
+        <v>4.8999999999999986</v>
+      </c>
+      <c r="O14" s="24">
+        <v>7.9</v>
+      </c>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3">
+      <c r="V14" s="3">
         <v>90.415000000000006</v>
       </c>
-      <c r="S14" s="3">
+      <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3">
+      <c r="X14" s="3">
         <v>11.6</v>
       </c>
-      <c r="U14" s="3">
+      <c r="Y14" s="3">
         <v>90.2</v>
       </c>
-      <c r="V14" s="3">
+      <c r="Z14" s="3">
         <f>188.7+116.9</f>
         <v>305.60000000000002</v>
       </c>
-      <c r="W14" s="3">
+      <c r="AA14" s="3">
         <f>24.5+2.5</f>
         <v>27</v>
       </c>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3"/>
+      <c r="AI14" s="3"/>
+      <c r="AJ14" s="3"/>
+      <c r="AK14" s="3"/>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>30</v>
       </c>
@@ -1855,7 +1977,7 @@
         <v>20.899999999999977</v>
       </c>
       <c r="I15" s="3">
-        <f t="shared" ref="I15:M15" si="6">I12-SUM(I13:I14)</f>
+        <f t="shared" ref="I15:O15" si="6">I12-SUM(I13:I14)</f>
         <v>32.699999999999818</v>
       </c>
       <c r="J15" s="3">
@@ -1874,52 +1996,62 @@
         <f t="shared" si="6"/>
         <v>167.40000000000009</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3">
-        <f t="shared" ref="P15:T15" si="7">P12-SUM(P13:P14)</f>
+      <c r="N15" s="3">
+        <f t="shared" si="6"/>
+        <v>210.5999999999998</v>
+      </c>
+      <c r="O15" s="3">
+        <f t="shared" si="6"/>
+        <v>198.69999999999993</v>
+      </c>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3">
+        <f t="shared" ref="T15:X15" si="7">T12-SUM(T13:T14)</f>
         <v>540.4109999999996</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="U15" s="3">
         <f t="shared" si="7"/>
         <v>566.67500000000064</v>
       </c>
-      <c r="R15" s="3">
+      <c r="V15" s="3">
         <f t="shared" si="7"/>
         <v>-85.118999999999687</v>
       </c>
-      <c r="S15" s="3">
+      <c r="W15" s="3">
         <f t="shared" si="7"/>
         <v>686.19999999999982</v>
       </c>
-      <c r="T15" s="3">
+      <c r="X15" s="3">
         <f t="shared" si="7"/>
         <v>646.50000000000045</v>
       </c>
-      <c r="U15" s="3">
-        <f>U12-SUM(U13:U14)</f>
+      <c r="Y15" s="3">
+        <f>Y12-SUM(Y13:Y14)</f>
         <v>353.30000000000018</v>
       </c>
-      <c r="V15" s="3">
-        <f>V12-SUM(V13:V14)</f>
+      <c r="Z15" s="3">
+        <f>Z12-SUM(Z13:Z14)</f>
         <v>264.10000000000036</v>
       </c>
-      <c r="W15" s="3">
-        <f>W12-SUM(W13:W14)</f>
+      <c r="AA15" s="3">
+        <f>AA12-SUM(AA13:AA14)</f>
         <v>677.60000000000036</v>
       </c>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
       <c r="AG15" s="3"/>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3"/>
+      <c r="AI15" s="3"/>
+      <c r="AJ15" s="3"/>
+      <c r="AK15" s="3"/>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
@@ -1933,7 +2065,7 @@
         <v>-11.5</v>
       </c>
       <c r="F16" s="3">
-        <f>+U16-SUM(C16:E16)</f>
+        <f>+Y16-SUM(C16:E16)</f>
         <v>-10.5</v>
       </c>
       <c r="G16" s="3">
@@ -1946,7 +2078,7 @@
         <v>-10.1</v>
       </c>
       <c r="J16" s="3">
-        <f>+V16-SUM(G16:I16)</f>
+        <f>+Z16-SUM(G16:I16)</f>
         <v>-11.399999999999999</v>
       </c>
       <c r="K16" s="3">
@@ -1958,44 +2090,53 @@
       <c r="M16" s="3">
         <v>-12.5</v>
       </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3">
+      <c r="N16" s="24">
+        <f>+AA16-SUM(K16:M16)</f>
+        <v>-13.399999999999999</v>
+      </c>
+      <c r="O16" s="24">
+        <v>-13.1</v>
+      </c>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3">
         <v>-55.295999999999999</v>
       </c>
-      <c r="Q16" s="3">
+      <c r="U16" s="3">
         <v>-66.248000000000005</v>
       </c>
-      <c r="R16" s="3">
+      <c r="V16" s="3">
         <v>-82.19</v>
       </c>
-      <c r="S16" s="3">
+      <c r="W16" s="3">
         <v>-72.900000000000006</v>
       </c>
-      <c r="T16" s="3">
+      <c r="X16" s="3">
         <v>-25.7</v>
       </c>
-      <c r="U16" s="3">
+      <c r="Y16" s="3">
         <v>-45.9</v>
       </c>
-      <c r="V16" s="3">
+      <c r="Z16" s="3">
         <v>-41.8</v>
       </c>
-      <c r="W16" s="3">
+      <c r="AA16" s="3">
         <v>-48.6</v>
       </c>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+    </row>
+    <row r="17" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>32</v>
       </c>
@@ -2009,7 +2150,7 @@
         <v>-26.7</v>
       </c>
       <c r="F17" s="3">
-        <f>+U17-SUM(C17:E17)</f>
+        <f>+Y17-SUM(C17:E17)</f>
         <v>-4.1000000000000014</v>
       </c>
       <c r="G17" s="3">
@@ -2022,7 +2163,7 @@
         <v>-0.4</v>
       </c>
       <c r="J17" s="3">
-        <f>+V17-SUM(G17:I17)</f>
+        <f>+Z17-SUM(G17:I17)</f>
         <v>-1</v>
       </c>
       <c r="K17" s="3">
@@ -2034,46 +2175,55 @@
       <c r="M17" s="3">
         <v>1.3</v>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3">
+      <c r="N17" s="24">
+        <f>+AA17-SUM(K17:M17)</f>
+        <v>1.5</v>
+      </c>
+      <c r="O17" s="24">
+        <v>42.6</v>
+      </c>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3">
         <v>14.907</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="U17" s="3">
         <f>-24.86+2.017</f>
         <v>-22.843</v>
       </c>
-      <c r="R17" s="3">
+      <c r="V17" s="3">
         <v>-22.474</v>
       </c>
-      <c r="S17" s="3">
+      <c r="W17" s="3">
         <f>-36.5+3.4</f>
         <v>-33.1</v>
       </c>
-      <c r="T17" s="3">
+      <c r="X17" s="3">
         <v>28.8</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Y17" s="3">
         <v>-42.2</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <v>-3.3</v>
       </c>
-      <c r="W17" s="3">
+      <c r="AA17" s="3">
         <v>5</v>
       </c>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3"/>
       <c r="AF17" s="3"/>
       <c r="AG17" s="3"/>
-    </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3"/>
+      <c r="AI17" s="3"/>
+      <c r="AJ17" s="3"/>
+      <c r="AK17" s="3"/>
+    </row>
+    <row r="18" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>33</v>
       </c>
@@ -2102,7 +2252,7 @@
         <v>10.999999999999977</v>
       </c>
       <c r="I18" s="3">
-        <f t="shared" ref="I18:M18" si="9">I15+I16+I17</f>
+        <f t="shared" ref="I18:O18" si="9">I15+I16+I17</f>
         <v>22.199999999999818</v>
       </c>
       <c r="J18" s="3">
@@ -2121,52 +2271,62 @@
         <f t="shared" si="9"/>
         <v>156.2000000000001</v>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3">
-        <f t="shared" ref="P18:T18" si="10">P15+P16+P17</f>
+      <c r="N18" s="3">
+        <f t="shared" si="9"/>
+        <v>198.69999999999979</v>
+      </c>
+      <c r="O18" s="3">
+        <f t="shared" si="9"/>
+        <v>228.19999999999993</v>
+      </c>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3">
+        <f t="shared" ref="T18:X18" si="10">T15+T16+T17</f>
         <v>500.02199999999959</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="U18" s="3">
         <f t="shared" si="10"/>
         <v>477.58400000000063</v>
       </c>
-      <c r="R18" s="3">
+      <c r="V18" s="3">
         <f t="shared" si="10"/>
         <v>-189.78299999999967</v>
       </c>
-      <c r="S18" s="3">
+      <c r="W18" s="3">
         <f t="shared" si="10"/>
         <v>580.19999999999982</v>
       </c>
-      <c r="T18" s="3">
+      <c r="X18" s="3">
         <f t="shared" si="10"/>
         <v>649.60000000000036</v>
       </c>
-      <c r="U18" s="3">
-        <f t="shared" ref="U18:W18" si="11">U15+U16+U17</f>
+      <c r="Y18" s="3">
+        <f t="shared" ref="Y18:AA18" si="11">Y15+Y16+Y17</f>
         <v>265.20000000000022</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Z18" s="3">
         <f t="shared" si="11"/>
         <v>219.00000000000034</v>
       </c>
-      <c r="W18" s="3">
+      <c r="AA18" s="3">
         <f t="shared" si="11"/>
         <v>634.00000000000034</v>
       </c>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3"/>
       <c r="AF18" s="3"/>
       <c r="AG18" s="3"/>
-    </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3"/>
+      <c r="AI18" s="3"/>
+      <c r="AJ18" s="3"/>
+      <c r="AK18" s="3"/>
+    </row>
+    <row r="19" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>35</v>
       </c>
@@ -2180,7 +2340,7 @@
         <v>-13</v>
       </c>
       <c r="F19" s="3">
-        <f>+U19-SUM(C19:E19)</f>
+        <f>+Y19-SUM(C19:E19)</f>
         <v>9.7000000000000011</v>
       </c>
       <c r="G19" s="3">
@@ -2193,7 +2353,7 @@
         <v>-0.5</v>
       </c>
       <c r="J19" s="3">
-        <f>+V19-SUM(G19:I19)</f>
+        <f>+Z19-SUM(G19:I19)</f>
         <v>17.200000000000003</v>
       </c>
       <c r="K19" s="3">
@@ -2205,37 +2365,46 @@
       <c r="M19" s="3">
         <v>34.200000000000003</v>
       </c>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3">
+      <c r="N19" s="24">
+        <f>+AA19-SUM(K19:M19)</f>
+        <v>38.5</v>
+      </c>
+      <c r="O19" s="24">
+        <v>51.1</v>
+      </c>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="24"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3">
         <v>214.77799999999999</v>
       </c>
-      <c r="Q19" s="3">
+      <c r="U19" s="3">
         <v>82.603999999999999</v>
       </c>
-      <c r="R19" s="3">
+      <c r="V19" s="3">
         <v>-62.642000000000003</v>
       </c>
-      <c r="S19" s="3">
+      <c r="W19" s="3">
         <v>26.7</v>
       </c>
-      <c r="T19" s="3">
+      <c r="X19" s="3">
         <v>80.5</v>
       </c>
-      <c r="U19" s="3">
+      <c r="Y19" s="3">
         <v>15.6</v>
       </c>
-      <c r="V19" s="3">
+      <c r="Z19" s="3">
         <v>8.4</v>
       </c>
-      <c r="W19" s="3">
+      <c r="AA19" s="3">
         <v>132</v>
       </c>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>51</v>
       </c>
@@ -2272,37 +2441,46 @@
       <c r="M20" s="3">
         <v>-96.1</v>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3">
+      <c r="N20" s="24">
+        <f>+AA20-SUM(K20:M20)</f>
+        <v>2.2000000000000028</v>
+      </c>
+      <c r="O20" s="24">
+        <v>1.3</v>
+      </c>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="24"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3">
         <v>2.1019999999999999</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="U20" s="3">
         <v>0.36799999999999999</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-76.099999999999994</v>
       </c>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-    </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="3"/>
+      <c r="AD20" s="3"/>
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>34</v>
       </c>
@@ -2350,45 +2528,55 @@
         <f>+M18-M19-M20</f>
         <v>218.10000000000008</v>
       </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3">
-        <f t="shared" ref="P21" si="13">P18-P19-P20</f>
+      <c r="N21" s="3">
+        <f>+N18-N19-N20</f>
+        <v>157.99999999999977</v>
+      </c>
+      <c r="O21" s="3">
+        <f>+O18-O19-O20</f>
+        <v>175.79999999999993</v>
+      </c>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3">
+        <f t="shared" ref="T21" si="13">T18-T19-T20</f>
         <v>283.1419999999996</v>
       </c>
-      <c r="Q21" s="3">
-        <f t="shared" ref="Q21" si="14">Q18-Q19-Q20</f>
+      <c r="U21" s="3">
+        <f t="shared" ref="U21" si="14">U18-U19-U20</f>
         <v>394.61200000000065</v>
       </c>
-      <c r="R21" s="3">
-        <f t="shared" ref="R21" si="15">R18-R19-R20</f>
+      <c r="V21" s="3">
+        <f t="shared" ref="V21" si="15">V18-V19-V20</f>
         <v>-127.14099999999968</v>
       </c>
-      <c r="S21" s="3">
-        <f t="shared" ref="S21" si="16">S18-S19-S20</f>
+      <c r="W21" s="3">
+        <f t="shared" ref="W21" si="16">W18-W19-W20</f>
         <v>553.49999999999977</v>
       </c>
-      <c r="T21" s="3">
-        <f t="shared" ref="T21" si="17">T18-T19-T20</f>
+      <c r="X21" s="3">
+        <f t="shared" ref="X21" si="17">X18-X19-X20</f>
         <v>569.10000000000036</v>
       </c>
-      <c r="U21" s="3">
-        <f t="shared" ref="U21:W21" si="18">U18-U19-U20</f>
+      <c r="Y21" s="3">
+        <f t="shared" ref="Y21:AA21" si="18">Y18-Y19-Y20</f>
         <v>249.60000000000022</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Z21" s="3">
         <f t="shared" si="18"/>
         <v>210.60000000000034</v>
       </c>
-      <c r="W21" s="3">
+      <c r="AA21" s="3">
         <f t="shared" si="18"/>
         <v>578.10000000000036</v>
       </c>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-    </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="3"/>
+      <c r="AD21" s="3"/>
+    </row>
+    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -2413,13 +2601,17 @@
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
-    </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+    </row>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C23" s="20">
-        <f t="shared" ref="C23:M23" si="19">C21/C24</f>
+        <f t="shared" ref="C23:O23" si="19">C21/C24</f>
         <v>0.2896785180133899</v>
       </c>
       <c r="D23" s="20">
@@ -2462,45 +2654,55 @@
         <f t="shared" si="19"/>
         <v>0.55123219224309916</v>
       </c>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="20">
-        <f t="shared" ref="P23:W23" si="20">P21/P24</f>
+      <c r="N23" s="20">
+        <f t="shared" si="19"/>
+        <v>0.39946947116888831</v>
+      </c>
+      <c r="O23" s="20">
+        <f t="shared" si="19"/>
+        <v>0.45087586869263624</v>
+      </c>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20">
+        <f t="shared" ref="T23:AA23" si="20">T21/T24</f>
         <v>0.75076129518607881</v>
       </c>
-      <c r="Q23" s="20">
+      <c r="U23" s="20">
         <f t="shared" si="20"/>
         <v>1.0142122202086339</v>
       </c>
-      <c r="R23" s="20">
+      <c r="V23" s="20">
         <f t="shared" si="20"/>
         <v>-0.32000040914627387</v>
       </c>
-      <c r="S23" s="20">
+      <c r="W23" s="20">
         <f t="shared" si="20"/>
         <v>1.378117770483809</v>
       </c>
-      <c r="T23" s="20">
+      <c r="X23" s="20">
         <f t="shared" si="20"/>
         <v>1.4322705277807677</v>
       </c>
-      <c r="U23" s="20">
+      <c r="Y23" s="20">
         <f t="shared" si="20"/>
         <v>0.62838528885085576</v>
       </c>
-      <c r="V23" s="20">
+      <c r="Z23" s="20">
         <f t="shared" si="20"/>
         <v>0.52887995981918723</v>
       </c>
-      <c r="W23" s="20">
+      <c r="AA23" s="20">
         <f t="shared" si="20"/>
         <v>1.4616031726755367</v>
       </c>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
-    </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
+      <c r="AD23" s="3"/>
+    </row>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>4</v>
       </c>
@@ -2514,7 +2716,7 @@
         <v>397.76739400000002</v>
       </c>
       <c r="F24" s="3">
-        <f>+U24</f>
+        <f>+Y24</f>
         <v>397.20853499999998</v>
       </c>
       <c r="G24" s="3">
@@ -2527,7 +2729,7 @@
         <v>398.187049</v>
       </c>
       <c r="J24" s="3">
-        <f>+V24</f>
+        <f>+Z24</f>
         <v>398.2</v>
       </c>
       <c r="K24" s="3">
@@ -2539,37 +2741,45 @@
       <c r="M24" s="3">
         <v>395.65904</v>
       </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3">
+      <c r="N24" s="3">
+        <v>395.52459299999998</v>
+      </c>
+      <c r="O24" s="3">
+        <v>389.90776</v>
+      </c>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3">
         <v>377.13984699999997</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="U24" s="3">
         <v>389.08227699999998</v>
       </c>
-      <c r="R24" s="3">
+      <c r="V24" s="3">
         <v>397.31511699999999</v>
       </c>
-      <c r="S24" s="3">
+      <c r="W24" s="3">
         <v>401.63476000000003</v>
       </c>
-      <c r="T24" s="3">
+      <c r="X24" s="3">
         <v>397.341137</v>
       </c>
-      <c r="U24" s="3">
+      <c r="Y24" s="3">
         <v>397.20853499999998</v>
       </c>
-      <c r="V24" s="3">
+      <c r="Z24" s="3">
         <v>398.2</v>
       </c>
-      <c r="W24" s="3">
+      <c r="AA24" s="3">
         <v>395.52459299999998</v>
       </c>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
-    </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+    </row>
+    <row r="25" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -2594,8 +2804,12 @@
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
-    </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+    </row>
+    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="2" t="s">
         <v>59</v>
@@ -2625,7 +2839,7 @@
         <v>3.1482232130793264E-2</v>
       </c>
       <c r="L26" s="21">
-        <f t="shared" ref="L26:N28" si="26">L8/H8-1</f>
+        <f t="shared" ref="L26:O28" si="26">L8/H8-1</f>
         <v>6.2825250773059782E-2</v>
       </c>
       <c r="M26" s="21">
@@ -2633,23 +2847,30 @@
         <v>7.0522361613154727E-2</v>
       </c>
       <c r="N26" s="21" t="e">
-        <f t="shared" ref="N26:N27" si="28">N8/J8-1</f>
+        <f t="shared" ref="N26:O27" si="28">N8/J8-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="O26" s="3"/>
+      <c r="O26" s="21">
+        <f t="shared" si="28"/>
+        <v>0.11291590254126294</v>
+      </c>
       <c r="P26" s="21"/>
       <c r="Q26" s="21"/>
       <c r="R26" s="21"/>
-      <c r="S26" s="21"/>
+      <c r="S26" s="3"/>
       <c r="T26" s="21"/>
       <c r="U26" s="21"/>
       <c r="V26" s="21"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="3"/>
-    </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="W26" s="21"/>
+      <c r="X26" s="21"/>
+      <c r="Y26" s="21"/>
+      <c r="Z26" s="21"/>
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="3"/>
+      <c r="AC26" s="3"/>
+      <c r="AD26" s="3"/>
+    </row>
+    <row r="27" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="2" t="s">
         <v>60</v>
@@ -2690,20 +2911,27 @@
         <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O27" s="3"/>
+      <c r="O27" s="21">
+        <f t="shared" si="28"/>
+        <v>0.23011363636363624</v>
+      </c>
       <c r="P27" s="21"/>
       <c r="Q27" s="21"/>
       <c r="R27" s="21"/>
-      <c r="S27" s="21"/>
+      <c r="S27" s="3"/>
       <c r="T27" s="21"/>
       <c r="U27" s="21"/>
       <c r="V27" s="21"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="3"/>
-    </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="W27" s="21"/>
+      <c r="X27" s="21"/>
+      <c r="Y27" s="21"/>
+      <c r="Z27" s="21"/>
+      <c r="AA27" s="3"/>
+      <c r="AB27" s="3"/>
+      <c r="AC27" s="3"/>
+      <c r="AD27" s="3"/>
+    </row>
+    <row r="28" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="s">
         <v>41</v>
       </c>
@@ -2741,46 +2969,53 @@
       </c>
       <c r="N28" s="22">
         <f t="shared" si="26"/>
-        <v>-1</v>
-      </c>
-      <c r="O28" s="3"/>
-      <c r="P28" s="22" t="e">
-        <f t="shared" ref="P28:U28" si="30">P10/O10-1</f>
+        <v>-0.11524200821725672</v>
+      </c>
+      <c r="O28" s="22">
+        <f t="shared" si="26"/>
+        <v>0.14127587110296047</v>
+      </c>
+      <c r="P28" s="22"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="22"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="22" t="e">
+        <f t="shared" ref="T28:Y28" si="30">T10/S10-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q28" s="22">
+      <c r="U28" s="22">
         <f t="shared" si="30"/>
         <v>3.3655998450346614E-2</v>
       </c>
-      <c r="R28" s="22">
+      <c r="V28" s="22">
         <f t="shared" si="30"/>
         <v>-0.22739167394141369</v>
       </c>
-      <c r="S28" s="22">
+      <c r="W28" s="22">
         <f t="shared" si="30"/>
         <v>0.29449947210725202</v>
       </c>
-      <c r="T28" s="22">
+      <c r="X28" s="22">
         <f t="shared" si="30"/>
         <v>7.0212876698069193E-2</v>
       </c>
-      <c r="U28" s="22">
+      <c r="Y28" s="22">
         <f t="shared" si="30"/>
         <v>1.685957915896541E-3</v>
       </c>
-      <c r="V28" s="22">
-        <f>V10/U10-1</f>
+      <c r="Z28" s="22">
+        <f>Z10/Y10-1</f>
         <v>2.8532124939310677E-2</v>
       </c>
-      <c r="W28" s="22">
-        <f>W10/V10-1</f>
+      <c r="AA28" s="22">
+        <f>AA10/Z10-1</f>
         <v>-1.1533680550092074E-2</v>
       </c>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
-    </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="3"/>
+      <c r="AD28" s="3"/>
+    </row>
+    <row r="29" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>42</v>
       </c>
@@ -2828,65 +3063,72 @@
         <f t="shared" si="33"/>
         <v>0.61656083970454845</v>
       </c>
-      <c r="N29" s="21" t="e">
+      <c r="N29" s="21">
         <f t="shared" si="33"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O29" s="3"/>
-      <c r="P29" s="21">
-        <f t="shared" ref="P29:V29" si="34">P12/P10</f>
+        <v>0.60754332313965342</v>
+      </c>
+      <c r="O29" s="21">
+        <f t="shared" ref="O29" si="34">O12/O10</f>
+        <v>0.61882352941176466</v>
+      </c>
+      <c r="P29" s="21"/>
+      <c r="Q29" s="21"/>
+      <c r="R29" s="21"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="21">
+        <f t="shared" ref="T29:Z29" si="35">T12/T10</f>
         <v>0.53771092505703577</v>
       </c>
-      <c r="Q29" s="21">
-        <f t="shared" si="34"/>
+      <c r="U29" s="21">
+        <f t="shared" si="35"/>
         <v>0.53814440073523095</v>
       </c>
-      <c r="R29" s="21">
-        <f t="shared" si="34"/>
+      <c r="V29" s="21">
+        <f t="shared" si="35"/>
         <v>0.52843714774865702</v>
       </c>
-      <c r="S29" s="21">
-        <f t="shared" si="34"/>
+      <c r="W29" s="21">
+        <f t="shared" si="35"/>
         <v>0.58063116986762431</v>
       </c>
-      <c r="T29" s="21">
-        <f t="shared" si="34"/>
+      <c r="X29" s="21">
+        <f t="shared" si="35"/>
         <v>0.57530071653211423</v>
       </c>
-      <c r="U29" s="21">
-        <f t="shared" si="34"/>
+      <c r="Y29" s="21">
+        <f t="shared" si="35"/>
         <v>0.56897556238873603</v>
       </c>
-      <c r="V29" s="21">
-        <f t="shared" si="34"/>
+      <c r="Z29" s="21">
+        <f t="shared" si="35"/>
         <v>0.60042798923732943</v>
       </c>
-      <c r="W29" s="21">
-        <f t="shared" ref="W29" si="35">W12/W10</f>
+      <c r="AA29" s="21">
+        <f t="shared" ref="AA29" si="36">AA12/AA10</f>
         <v>0.6172874880611271</v>
       </c>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="3"/>
-    </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3"/>
+      <c r="AC29" s="3"/>
+      <c r="AD29" s="3"/>
+    </row>
+    <row r="30" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="21">
-        <f t="shared" ref="C30:F30" si="36">C15/C10</f>
+        <f t="shared" ref="C30:F30" si="37">C15/C10</f>
         <v>9.3196755284504759E-2</v>
       </c>
       <c r="D30" s="21">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>7.4057450628366083E-3</v>
       </c>
       <c r="E30" s="21">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2.3031105228325584E-2</v>
       </c>
       <c r="F30" s="21">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>9.2066004992997844E-2</v>
       </c>
       <c r="G30" s="21">
@@ -2894,88 +3136,95 @@
         <v>-2.5680534155123568E-4</v>
       </c>
       <c r="H30" s="21">
-        <f t="shared" ref="H30:J30" si="37">H15/H10</f>
+        <f t="shared" ref="H30:J30" si="38">H15/H10</f>
         <v>1.5381218722402104E-2</v>
       </c>
       <c r="I30" s="21">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>2.2659552352574195E-2</v>
       </c>
       <c r="J30" s="21">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.10567191101312771</v>
       </c>
       <c r="K30" s="21">
-        <f t="shared" ref="K30:N30" si="38">K15/K10</f>
+        <f t="shared" ref="K30:N30" si="39">K15/K10</f>
         <v>0.12549122347393235</v>
       </c>
       <c r="L30" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>7.4688796680497924E-2</v>
       </c>
       <c r="M30" s="21">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.10846183750161985</v>
       </c>
-      <c r="N30" s="21" t="e">
-        <f t="shared" si="38"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O30" s="3"/>
-      <c r="P30" s="21">
-        <f t="shared" ref="P30:V30" si="39">P15/P10</f>
+      <c r="N30" s="21">
+        <f t="shared" si="39"/>
+        <v>0.1192660550458715</v>
+      </c>
+      <c r="O30" s="21">
+        <f t="shared" ref="O30" si="40">O15/O10</f>
+        <v>0.11403156384505017</v>
+      </c>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="21"/>
+      <c r="R30" s="21"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="21">
+        <f t="shared" ref="T30:Z30" si="41">T15/T10</f>
         <v>9.6927058671602534E-2</v>
       </c>
-      <c r="Q30" s="21">
-        <f t="shared" si="39"/>
+      <c r="U30" s="21">
+        <f t="shared" si="41"/>
         <v>9.8328378523524038E-2</v>
       </c>
-      <c r="R30" s="21">
-        <f t="shared" si="39"/>
+      <c r="V30" s="21">
+        <f t="shared" si="41"/>
         <v>-1.9116657222765277E-2</v>
       </c>
-      <c r="S30" s="21">
-        <f t="shared" si="39"/>
+      <c r="W30" s="21">
+        <f t="shared" si="41"/>
         <v>0.1190513367685074</v>
       </c>
-      <c r="T30" s="21">
-        <f t="shared" si="39"/>
+      <c r="X30" s="21">
+        <f t="shared" si="41"/>
         <v>0.10480498006030549</v>
       </c>
-      <c r="U30" s="21">
-        <f t="shared" si="39"/>
+      <c r="Y30" s="21">
+        <f t="shared" si="41"/>
         <v>5.7177536818255409E-2</v>
       </c>
-      <c r="V30" s="21">
-        <f t="shared" si="39"/>
+      <c r="Z30" s="21">
+        <f t="shared" si="41"/>
         <v>4.1555866756880139E-2</v>
       </c>
-      <c r="W30" s="21">
-        <f t="shared" ref="W30" si="40">W15/W10</f>
+      <c r="AA30" s="21">
+        <f t="shared" ref="AA30" si="42">AA15/AA10</f>
         <v>0.10786373766316465</v>
       </c>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
-      <c r="Z30" s="3"/>
-    </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3"/>
+      <c r="AC30" s="3"/>
+      <c r="AD30" s="3"/>
+    </row>
+    <row r="31" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C31" s="21">
-        <f t="shared" ref="C31:F31" si="41">C21/C10</f>
+        <f t="shared" ref="C31:F31" si="43">C21/C10</f>
         <v>6.7914026881402148E-2</v>
       </c>
       <c r="D31" s="21">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>-1.196888090963512E-3</v>
       </c>
       <c r="E31" s="21">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>6.3534083388484151E-3</v>
       </c>
       <c r="F31" s="21">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>7.7269682761980374E-2</v>
       </c>
       <c r="G31" s="21">
@@ -2983,88 +3232,95 @@
         <v>-6.8053415511043951E-3</v>
       </c>
       <c r="H31" s="21">
-        <f t="shared" ref="H31:J31" si="42">H21/H10</f>
+        <f t="shared" ref="H31:J31" si="44">H21/H10</f>
         <v>1.3246982631733868E-2</v>
       </c>
       <c r="I31" s="21">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>1.4344120296583619E-2</v>
       </c>
       <c r="J31" s="21">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>9.0840765607776472E-2</v>
       </c>
       <c r="K31" s="21">
-        <f t="shared" ref="K31:N31" si="43">K21/K10</f>
+        <f t="shared" ref="K31:N31" si="45">K21/K10</f>
         <v>8.8420225307833319E-2</v>
       </c>
       <c r="L31" s="21">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>4.6334716459197789E-2</v>
       </c>
       <c r="M31" s="21">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>0.14131139043669824</v>
       </c>
-      <c r="N31" s="21" t="e">
-        <f t="shared" si="43"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O31" s="3"/>
-      <c r="P31" s="21">
-        <f t="shared" ref="P31:V31" si="44">P21/P10</f>
+      <c r="N31" s="21">
+        <f t="shared" si="45"/>
+        <v>8.9477857061954824E-2</v>
+      </c>
+      <c r="O31" s="21">
+        <f t="shared" ref="O31" si="46">O21/O10</f>
+        <v>0.10088952654232421</v>
+      </c>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="21"/>
+      <c r="R31" s="21"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="21">
+        <f t="shared" ref="T31:Z31" si="47">T21/T10</f>
         <v>5.0783794642216509E-2</v>
       </c>
-      <c r="Q31" s="21">
-        <f t="shared" si="44"/>
+      <c r="U31" s="21">
+        <f t="shared" si="47"/>
         <v>6.8472330887942634E-2</v>
       </c>
-      <c r="R31" s="21">
-        <f t="shared" si="44"/>
+      <c r="V31" s="21">
+        <f t="shared" si="47"/>
         <v>-2.8554270091984198E-2</v>
       </c>
-      <c r="S31" s="21">
-        <f t="shared" si="44"/>
+      <c r="W31" s="21">
+        <f t="shared" si="47"/>
         <v>9.6028730547025418E-2</v>
       </c>
-      <c r="T31" s="21">
-        <f t="shared" si="44"/>
+      <c r="X31" s="21">
+        <f t="shared" si="47"/>
         <v>9.2257562493920878E-2</v>
       </c>
-      <c r="U31" s="21">
-        <f t="shared" si="44"/>
+      <c r="Y31" s="21">
+        <f t="shared" si="47"/>
         <v>4.0394885903867979E-2</v>
       </c>
-      <c r="V31" s="21">
-        <f t="shared" si="44"/>
+      <c r="Z31" s="21">
+        <f t="shared" si="47"/>
         <v>3.3137696096171752E-2</v>
       </c>
-      <c r="W31" s="21">
-        <f t="shared" ref="W31" si="45">W21/W10</f>
+      <c r="AA31" s="21">
+        <f t="shared" ref="AA31" si="48">AA21/AA10</f>
         <v>9.2024832855778477E-2</v>
       </c>
-      <c r="X31" s="3"/>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="3"/>
-    </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3"/>
+      <c r="AC31" s="3"/>
+      <c r="AD31" s="3"/>
+    </row>
+    <row r="32" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C32" s="21">
-        <f t="shared" ref="C32:F32" si="46">C19/C18</f>
+        <f t="shared" ref="C32:F32" si="49">C19/C18</f>
         <v>0.17600574712643666</v>
       </c>
       <c r="D32" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>0.77777777777777535</v>
       </c>
       <c r="E32" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>3.8235294117646554</v>
       </c>
       <c r="F32" s="21">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>7.1010248901903175E-2</v>
       </c>
       <c r="G32" s="21">
@@ -3072,71 +3328,78 @@
         <v>0.16535433070865876</v>
       </c>
       <c r="H32" s="21">
-        <f t="shared" ref="H32:J32" si="47">H19/H18</f>
+        <f t="shared" ref="H32:J32" si="50">H19/H18</f>
         <v>-0.56363636363636482</v>
       </c>
       <c r="I32" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>-2.2522522522522705E-2</v>
       </c>
       <c r="J32" s="21">
-        <f t="shared" si="47"/>
+        <f t="shared" si="50"/>
         <v>8.6649874055415493E-2</v>
       </c>
       <c r="K32" s="21">
-        <f t="shared" ref="K32:N32" si="48">K19/K18</f>
+        <f t="shared" ref="K32:N32" si="51">K19/K18</f>
         <v>0.20611551528878833</v>
       </c>
       <c r="L32" s="21">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>0.22341463414634144</v>
       </c>
       <c r="M32" s="21">
-        <f t="shared" si="48"/>
+        <f t="shared" si="51"/>
         <v>0.21895006402048642</v>
       </c>
-      <c r="N32" s="21" t="e">
-        <f t="shared" si="48"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O32" s="3"/>
-      <c r="P32" s="21">
-        <f t="shared" ref="P32:V32" si="49">P19/P18</f>
+      <c r="N32" s="21">
+        <f t="shared" si="51"/>
+        <v>0.19375943633618542</v>
+      </c>
+      <c r="O32" s="21">
+        <f t="shared" ref="O32" si="52">O19/O18</f>
+        <v>0.22392638036809823</v>
+      </c>
+      <c r="P32" s="21"/>
+      <c r="Q32" s="21"/>
+      <c r="R32" s="21"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="21">
+        <f t="shared" ref="T32:Z32" si="53">T19/T18</f>
         <v>0.42953710036758413</v>
       </c>
-      <c r="Q32" s="21">
-        <f t="shared" si="49"/>
+      <c r="U32" s="21">
+        <f t="shared" si="53"/>
         <v>0.1729622432912323</v>
       </c>
-      <c r="R32" s="21">
-        <f t="shared" si="49"/>
+      <c r="V32" s="21">
+        <f t="shared" si="53"/>
         <v>0.33007171348329467</v>
       </c>
-      <c r="S32" s="21">
-        <f t="shared" si="49"/>
+      <c r="W32" s="21">
+        <f t="shared" si="53"/>
         <v>4.6018614270941068E-2</v>
       </c>
-      <c r="T32" s="21">
-        <f t="shared" si="49"/>
+      <c r="X32" s="21">
+        <f t="shared" si="53"/>
         <v>0.12392241379310338</v>
       </c>
-      <c r="U32" s="21">
-        <f t="shared" si="49"/>
+      <c r="Y32" s="21">
+        <f t="shared" si="53"/>
         <v>5.8823529411764656E-2</v>
       </c>
-      <c r="V32" s="21">
-        <f t="shared" si="49"/>
+      <c r="Z32" s="21">
+        <f t="shared" si="53"/>
         <v>3.8356164383561583E-2</v>
       </c>
-      <c r="W32" s="21">
-        <f t="shared" ref="W32" si="50">W19/W18</f>
+      <c r="AA32" s="21">
+        <f t="shared" ref="AA32" si="54">AA19/AA18</f>
         <v>0.20820189274447939</v>
       </c>
-      <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="3"/>
-    </row>
-    <row r="33" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3"/>
+      <c r="AC32" s="3"/>
+      <c r="AD32" s="3"/>
+    </row>
+    <row r="33" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -3161,8 +3424,12 @@
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
-    </row>
-    <row r="34" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3"/>
+      <c r="AB33" s="3"/>
+      <c r="AC33" s="3"/>
+      <c r="AD33" s="3"/>
+    </row>
+    <row r="34" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -3187,8 +3454,12 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
-    </row>
-    <row r="35" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3"/>
+      <c r="AB34" s="3"/>
+      <c r="AC34" s="3"/>
+      <c r="AD34" s="3"/>
+    </row>
+    <row r="35" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -3213,8 +3484,12 @@
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
-    </row>
-    <row r="36" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3"/>
+      <c r="AB35" s="3"/>
+      <c r="AC35" s="3"/>
+      <c r="AD35" s="3"/>
+    </row>
+    <row r="36" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -3239,8 +3514,12 @@
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
-    </row>
-    <row r="37" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA36" s="3"/>
+      <c r="AB36" s="3"/>
+      <c r="AC36" s="3"/>
+      <c r="AD36" s="3"/>
+    </row>
+    <row r="37" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -3265,8 +3544,12 @@
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
-    </row>
-    <row r="38" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA37" s="3"/>
+      <c r="AB37" s="3"/>
+      <c r="AC37" s="3"/>
+      <c r="AD37" s="3"/>
+    </row>
+    <row r="38" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -3291,8 +3574,12 @@
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
-    </row>
-    <row r="39" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="3"/>
+      <c r="AB38" s="3"/>
+      <c r="AC38" s="3"/>
+      <c r="AD38" s="3"/>
+    </row>
+    <row r="39" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -3317,8 +3604,12 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -3343,8 +3634,12 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -3369,8 +3664,12 @@
       <c r="X41" s="3"/>
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
-    </row>
-    <row r="42" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3"/>
+      <c r="AB41" s="3"/>
+      <c r="AC41" s="3"/>
+      <c r="AD41" s="3"/>
+    </row>
+    <row r="42" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -3395,8 +3694,12 @@
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
-    </row>
-    <row r="43" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3"/>
+      <c r="AB42" s="3"/>
+      <c r="AC42" s="3"/>
+      <c r="AD42" s="3"/>
+    </row>
+    <row r="43" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -3421,8 +3724,12 @@
       <c r="X43" s="3"/>
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
-    </row>
-    <row r="44" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3"/>
+      <c r="AB43" s="3"/>
+      <c r="AC43" s="3"/>
+      <c r="AD43" s="3"/>
+    </row>
+    <row r="44" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -3447,8 +3754,12 @@
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
-    </row>
-    <row r="45" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3"/>
+      <c r="AB44" s="3"/>
+      <c r="AC44" s="3"/>
+      <c r="AD44" s="3"/>
+    </row>
+    <row r="45" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -3473,8 +3784,12 @@
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
-    </row>
-    <row r="46" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3"/>
+      <c r="AB45" s="3"/>
+      <c r="AC45" s="3"/>
+      <c r="AD45" s="3"/>
+    </row>
+    <row r="46" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -3499,8 +3814,12 @@
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
-    </row>
-    <row r="47" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3"/>
+      <c r="AB46" s="3"/>
+      <c r="AC46" s="3"/>
+      <c r="AD46" s="3"/>
+    </row>
+    <row r="47" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -3525,8 +3844,12 @@
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
-    </row>
-    <row r="48" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3"/>
+      <c r="AB47" s="3"/>
+      <c r="AC47" s="3"/>
+      <c r="AD47" s="3"/>
+    </row>
+    <row r="48" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -3551,8 +3874,12 @@
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3"/>
+      <c r="AB48" s="3"/>
+      <c r="AC48" s="3"/>
+      <c r="AD48" s="3"/>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -3577,8 +3904,12 @@
       <c r="X49" s="3"/>
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3"/>
+      <c r="AB49" s="3"/>
+      <c r="AC49" s="3"/>
+      <c r="AD49" s="3"/>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -3603,8 +3934,12 @@
       <c r="X50" s="3"/>
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3"/>
+      <c r="AB50" s="3"/>
+      <c r="AC50" s="3"/>
+      <c r="AD50" s="3"/>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -3629,8 +3964,12 @@
       <c r="X51" s="3"/>
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3"/>
+      <c r="AB51" s="3"/>
+      <c r="AC51" s="3"/>
+      <c r="AD51" s="3"/>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -3655,8 +3994,12 @@
       <c r="X52" s="3"/>
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3"/>
+      <c r="AB52" s="3"/>
+      <c r="AC52" s="3"/>
+      <c r="AD52" s="3"/>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -3681,8 +4024,12 @@
       <c r="X53" s="3"/>
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3"/>
+      <c r="AB53" s="3"/>
+      <c r="AC53" s="3"/>
+      <c r="AD53" s="3"/>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -3707,8 +4054,12 @@
       <c r="X54" s="3"/>
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3"/>
+      <c r="AB54" s="3"/>
+      <c r="AC54" s="3"/>
+      <c r="AD54" s="3"/>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -3733,8 +4084,12 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -3759,8 +4114,12 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -3785,8 +4144,12 @@
       <c r="X57" s="3"/>
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3"/>
+      <c r="AB57" s="3"/>
+      <c r="AC57" s="3"/>
+      <c r="AD57" s="3"/>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -3811,8 +4174,12 @@
       <c r="X58" s="3"/>
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3"/>
+      <c r="AB58" s="3"/>
+      <c r="AC58" s="3"/>
+      <c r="AD58" s="3"/>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -3837,8 +4204,12 @@
       <c r="X59" s="3"/>
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3"/>
+      <c r="AB59" s="3"/>
+      <c r="AC59" s="3"/>
+      <c r="AD59" s="3"/>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -3863,8 +4234,12 @@
       <c r="X60" s="3"/>
       <c r="Y60" s="3"/>
       <c r="Z60" s="3"/>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3"/>
+      <c r="AB60" s="3"/>
+      <c r="AC60" s="3"/>
+      <c r="AD60" s="3"/>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -3889,8 +4264,12 @@
       <c r="X61" s="3"/>
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3"/>
+      <c r="AB61" s="3"/>
+      <c r="AC61" s="3"/>
+      <c r="AD61" s="3"/>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -3915,8 +4294,12 @@
       <c r="X62" s="3"/>
       <c r="Y62" s="3"/>
       <c r="Z62" s="3"/>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3"/>
+      <c r="AB62" s="3"/>
+      <c r="AC62" s="3"/>
+      <c r="AD62" s="3"/>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -3941,8 +4324,12 @@
       <c r="X63" s="3"/>
       <c r="Y63" s="3"/>
       <c r="Z63" s="3"/>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3"/>
+      <c r="AB63" s="3"/>
+      <c r="AC63" s="3"/>
+      <c r="AD63" s="3"/>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -3967,8 +4354,12 @@
       <c r="X64" s="3"/>
       <c r="Y64" s="3"/>
       <c r="Z64" s="3"/>
-    </row>
-    <row r="65" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3"/>
+      <c r="AB64" s="3"/>
+      <c r="AC64" s="3"/>
+      <c r="AD64" s="3"/>
+    </row>
+    <row r="65" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -3993,8 +4384,12 @@
       <c r="X65" s="3"/>
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
-    </row>
-    <row r="66" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3"/>
+      <c r="AB65" s="3"/>
+      <c r="AC65" s="3"/>
+      <c r="AD65" s="3"/>
+    </row>
+    <row r="66" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -4019,8 +4414,12 @@
       <c r="X66" s="3"/>
       <c r="Y66" s="3"/>
       <c r="Z66" s="3"/>
-    </row>
-    <row r="67" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3"/>
+      <c r="AB66" s="3"/>
+      <c r="AC66" s="3"/>
+      <c r="AD66" s="3"/>
+    </row>
+    <row r="67" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -4045,8 +4444,12 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -4071,8 +4474,12 @@
       <c r="X68" s="3"/>
       <c r="Y68" s="3"/>
       <c r="Z68" s="3"/>
-    </row>
-    <row r="69" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3"/>
+      <c r="AB68" s="3"/>
+      <c r="AC68" s="3"/>
+      <c r="AD68" s="3"/>
+    </row>
+    <row r="69" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -4097,8 +4504,12 @@
       <c r="X69" s="3"/>
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
-    </row>
-    <row r="70" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3"/>
+      <c r="AB69" s="3"/>
+      <c r="AC69" s="3"/>
+      <c r="AD69" s="3"/>
+    </row>
+    <row r="70" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -4123,8 +4534,12 @@
       <c r="X70" s="3"/>
       <c r="Y70" s="3"/>
       <c r="Z70" s="3"/>
-    </row>
-    <row r="71" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3"/>
+      <c r="AB70" s="3"/>
+      <c r="AC70" s="3"/>
+      <c r="AD70" s="3"/>
+    </row>
+    <row r="71" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -4149,8 +4564,12 @@
       <c r="X71" s="3"/>
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
-    </row>
-    <row r="72" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3"/>
+      <c r="AB71" s="3"/>
+      <c r="AC71" s="3"/>
+      <c r="AD71" s="3"/>
+    </row>
+    <row r="72" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -4175,8 +4594,12 @@
       <c r="X72" s="3"/>
       <c r="Y72" s="3"/>
       <c r="Z72" s="3"/>
-    </row>
-    <row r="73" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3"/>
+      <c r="AB72" s="3"/>
+      <c r="AC72" s="3"/>
+      <c r="AD72" s="3"/>
+    </row>
+    <row r="73" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -4201,8 +4624,12 @@
       <c r="X73" s="3"/>
       <c r="Y73" s="3"/>
       <c r="Z73" s="3"/>
-    </row>
-    <row r="74" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3"/>
+      <c r="AB73" s="3"/>
+      <c r="AC73" s="3"/>
+      <c r="AD73" s="3"/>
+    </row>
+    <row r="74" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -4227,8 +4654,12 @@
       <c r="X74" s="3"/>
       <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
-    </row>
-    <row r="75" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3"/>
+      <c r="AB74" s="3"/>
+      <c r="AC74" s="3"/>
+      <c r="AD74" s="3"/>
+    </row>
+    <row r="75" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -4253,8 +4684,12 @@
       <c r="X75" s="3"/>
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
-    </row>
-    <row r="76" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3"/>
+      <c r="AB75" s="3"/>
+      <c r="AC75" s="3"/>
+      <c r="AD75" s="3"/>
+    </row>
+    <row r="76" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -4279,8 +4714,12 @@
       <c r="X76" s="3"/>
       <c r="Y76" s="3"/>
       <c r="Z76" s="3"/>
-    </row>
-    <row r="77" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3"/>
+      <c r="AB76" s="3"/>
+      <c r="AC76" s="3"/>
+      <c r="AD76" s="3"/>
+    </row>
+    <row r="77" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -4305,8 +4744,12 @@
       <c r="X77" s="3"/>
       <c r="Y77" s="3"/>
       <c r="Z77" s="3"/>
-    </row>
-    <row r="78" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3"/>
+      <c r="AB77" s="3"/>
+      <c r="AC77" s="3"/>
+      <c r="AD77" s="3"/>
+    </row>
+    <row r="78" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -4331,8 +4774,12 @@
       <c r="X78" s="3"/>
       <c r="Y78" s="3"/>
       <c r="Z78" s="3"/>
-    </row>
-    <row r="79" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA78" s="3"/>
+      <c r="AB78" s="3"/>
+      <c r="AC78" s="3"/>
+      <c r="AD78" s="3"/>
+    </row>
+    <row r="79" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -4357,8 +4804,12 @@
       <c r="X79" s="3"/>
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
-    </row>
-    <row r="80" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA79" s="3"/>
+      <c r="AB79" s="3"/>
+      <c r="AC79" s="3"/>
+      <c r="AD79" s="3"/>
+    </row>
+    <row r="80" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -4383,8 +4834,12 @@
       <c r="X80" s="3"/>
       <c r="Y80" s="3"/>
       <c r="Z80" s="3"/>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="3"/>
+      <c r="AB80" s="3"/>
+      <c r="AC80" s="3"/>
+      <c r="AD80" s="3"/>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -4409,8 +4864,12 @@
       <c r="X81" s="3"/>
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3"/>
+      <c r="AB81" s="3"/>
+      <c r="AC81" s="3"/>
+      <c r="AD81" s="3"/>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -4435,8 +4894,12 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -4461,8 +4924,12 @@
       <c r="X83" s="3"/>
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3"/>
+      <c r="AB83" s="3"/>
+      <c r="AC83" s="3"/>
+      <c r="AD83" s="3"/>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -4487,8 +4954,12 @@
       <c r="X84" s="3"/>
       <c r="Y84" s="3"/>
       <c r="Z84" s="3"/>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3"/>
+      <c r="AB84" s="3"/>
+      <c r="AC84" s="3"/>
+      <c r="AD84" s="3"/>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -4513,8 +4984,12 @@
       <c r="X85" s="3"/>
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3"/>
+      <c r="AB85" s="3"/>
+      <c r="AC85" s="3"/>
+      <c r="AD85" s="3"/>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -4539,8 +5014,12 @@
       <c r="X86" s="3"/>
       <c r="Y86" s="3"/>
       <c r="Z86" s="3"/>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3"/>
+      <c r="AB86" s="3"/>
+      <c r="AC86" s="3"/>
+      <c r="AD86" s="3"/>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -4565,8 +5044,12 @@
       <c r="X87" s="3"/>
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3"/>
+      <c r="AB87" s="3"/>
+      <c r="AC87" s="3"/>
+      <c r="AD87" s="3"/>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -4591,8 +5074,12 @@
       <c r="X88" s="3"/>
       <c r="Y88" s="3"/>
       <c r="Z88" s="3"/>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3"/>
+      <c r="AB88" s="3"/>
+      <c r="AC88" s="3"/>
+      <c r="AD88" s="3"/>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -4617,8 +5104,12 @@
       <c r="X89" s="3"/>
       <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3"/>
+      <c r="AB89" s="3"/>
+      <c r="AC89" s="3"/>
+      <c r="AD89" s="3"/>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -4643,8 +5134,12 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -4669,8 +5164,12 @@
       <c r="X91" s="3"/>
       <c r="Y91" s="3"/>
       <c r="Z91" s="3"/>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3"/>
+      <c r="AB91" s="3"/>
+      <c r="AC91" s="3"/>
+      <c r="AD91" s="3"/>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -4695,8 +5194,12 @@
       <c r="X92" s="3"/>
       <c r="Y92" s="3"/>
       <c r="Z92" s="3"/>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3"/>
+      <c r="AB92" s="3"/>
+      <c r="AC92" s="3"/>
+      <c r="AD92" s="3"/>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -4721,8 +5224,12 @@
       <c r="X93" s="3"/>
       <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3"/>
+      <c r="AB93" s="3"/>
+      <c r="AC93" s="3"/>
+      <c r="AD93" s="3"/>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -4747,8 +5254,12 @@
       <c r="X94" s="3"/>
       <c r="Y94" s="3"/>
       <c r="Z94" s="3"/>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3"/>
+      <c r="AB94" s="3"/>
+      <c r="AC94" s="3"/>
+      <c r="AD94" s="3"/>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -4773,8 +5284,12 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -4799,8 +5314,12 @@
       <c r="X96" s="3"/>
       <c r="Y96" s="3"/>
       <c r="Z96" s="3"/>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3"/>
+      <c r="AB96" s="3"/>
+      <c r="AC96" s="3"/>
+      <c r="AD96" s="3"/>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -4825,8 +5344,12 @@
       <c r="X97" s="3"/>
       <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3"/>
+      <c r="AB97" s="3"/>
+      <c r="AC97" s="3"/>
+      <c r="AD97" s="3"/>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -4851,8 +5374,12 @@
       <c r="X98" s="3"/>
       <c r="Y98" s="3"/>
       <c r="Z98" s="3"/>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3"/>
+      <c r="AB98" s="3"/>
+      <c r="AC98" s="3"/>
+      <c r="AD98" s="3"/>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -4877,8 +5404,12 @@
       <c r="X99" s="3"/>
       <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3"/>
+      <c r="AB99" s="3"/>
+      <c r="AC99" s="3"/>
+      <c r="AD99" s="3"/>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -4903,8 +5434,12 @@
       <c r="X100" s="3"/>
       <c r="Y100" s="3"/>
       <c r="Z100" s="3"/>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3"/>
+      <c r="AB100" s="3"/>
+      <c r="AC100" s="3"/>
+      <c r="AD100" s="3"/>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -4929,8 +5464,12 @@
       <c r="X101" s="3"/>
       <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3"/>
+      <c r="AB101" s="3"/>
+      <c r="AC101" s="3"/>
+      <c r="AD101" s="3"/>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -4955,8 +5494,12 @@
       <c r="X102" s="3"/>
       <c r="Y102" s="3"/>
       <c r="Z102" s="3"/>
-    </row>
-    <row r="103" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA102" s="3"/>
+      <c r="AB102" s="3"/>
+      <c r="AC102" s="3"/>
+      <c r="AD102" s="3"/>
+    </row>
+    <row r="103" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -4981,8 +5524,12 @@
       <c r="X103" s="3"/>
       <c r="Y103" s="3"/>
       <c r="Z103" s="3"/>
-    </row>
-    <row r="104" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA103" s="3"/>
+      <c r="AB103" s="3"/>
+      <c r="AC103" s="3"/>
+      <c r="AD103" s="3"/>
+    </row>
+    <row r="104" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -5007,8 +5554,12 @@
       <c r="X104" s="3"/>
       <c r="Y104" s="3"/>
       <c r="Z104" s="3"/>
-    </row>
-    <row r="105" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA104" s="3"/>
+      <c r="AB104" s="3"/>
+      <c r="AC104" s="3"/>
+      <c r="AD104" s="3"/>
+    </row>
+    <row r="105" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -5033,8 +5584,12 @@
       <c r="X105" s="3"/>
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
-    </row>
-    <row r="106" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA105" s="3"/>
+      <c r="AB105" s="3"/>
+      <c r="AC105" s="3"/>
+      <c r="AD105" s="3"/>
+    </row>
+    <row r="106" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -5059,8 +5614,12 @@
       <c r="X106" s="3"/>
       <c r="Y106" s="3"/>
       <c r="Z106" s="3"/>
-    </row>
-    <row r="107" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA106" s="3"/>
+      <c r="AB106" s="3"/>
+      <c r="AC106" s="3"/>
+      <c r="AD106" s="3"/>
+    </row>
+    <row r="107" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -5085,8 +5644,12 @@
       <c r="X107" s="3"/>
       <c r="Y107" s="3"/>
       <c r="Z107" s="3"/>
-    </row>
-    <row r="108" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA107" s="3"/>
+      <c r="AB107" s="3"/>
+      <c r="AC107" s="3"/>
+      <c r="AD107" s="3"/>
+    </row>
+    <row r="108" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -5111,8 +5674,12 @@
       <c r="X108" s="3"/>
       <c r="Y108" s="3"/>
       <c r="Z108" s="3"/>
-    </row>
-    <row r="109" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA108" s="3"/>
+      <c r="AB108" s="3"/>
+      <c r="AC108" s="3"/>
+      <c r="AD108" s="3"/>
+    </row>
+    <row r="109" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -5137,8 +5704,12 @@
       <c r="X109" s="3"/>
       <c r="Y109" s="3"/>
       <c r="Z109" s="3"/>
-    </row>
-    <row r="110" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA109" s="3"/>
+      <c r="AB109" s="3"/>
+      <c r="AC109" s="3"/>
+      <c r="AD109" s="3"/>
+    </row>
+    <row r="110" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -5163,8 +5734,12 @@
       <c r="X110" s="3"/>
       <c r="Y110" s="3"/>
       <c r="Z110" s="3"/>
-    </row>
-    <row r="111" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA110" s="3"/>
+      <c r="AB110" s="3"/>
+      <c r="AC110" s="3"/>
+      <c r="AD110" s="3"/>
+    </row>
+    <row r="111" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -5189,8 +5764,12 @@
       <c r="X111" s="3"/>
       <c r="Y111" s="3"/>
       <c r="Z111" s="3"/>
-    </row>
-    <row r="112" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA111" s="3"/>
+      <c r="AB111" s="3"/>
+      <c r="AC111" s="3"/>
+      <c r="AD111" s="3"/>
+    </row>
+    <row r="112" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -5215,8 +5794,12 @@
       <c r="X112" s="3"/>
       <c r="Y112" s="3"/>
       <c r="Z112" s="3"/>
-    </row>
-    <row r="113" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA112" s="3"/>
+      <c r="AB112" s="3"/>
+      <c r="AC112" s="3"/>
+      <c r="AD112" s="3"/>
+    </row>
+    <row r="113" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -5241,8 +5824,12 @@
       <c r="X113" s="3"/>
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
-    </row>
-    <row r="114" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA113" s="3"/>
+      <c r="AB113" s="3"/>
+      <c r="AC113" s="3"/>
+      <c r="AD113" s="3"/>
+    </row>
+    <row r="114" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -5267,8 +5854,12 @@
       <c r="X114" s="3"/>
       <c r="Y114" s="3"/>
       <c r="Z114" s="3"/>
-    </row>
-    <row r="115" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA114" s="3"/>
+      <c r="AB114" s="3"/>
+      <c r="AC114" s="3"/>
+      <c r="AD114" s="3"/>
+    </row>
+    <row r="115" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -5293,8 +5884,12 @@
       <c r="X115" s="3"/>
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
-    </row>
-    <row r="116" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA115" s="3"/>
+      <c r="AB115" s="3"/>
+      <c r="AC115" s="3"/>
+      <c r="AD115" s="3"/>
+    </row>
+    <row r="116" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -5319,8 +5914,12 @@
       <c r="X116" s="3"/>
       <c r="Y116" s="3"/>
       <c r="Z116" s="3"/>
-    </row>
-    <row r="117" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA116" s="3"/>
+      <c r="AB116" s="3"/>
+      <c r="AC116" s="3"/>
+      <c r="AD116" s="3"/>
+    </row>
+    <row r="117" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -5345,8 +5944,12 @@
       <c r="X117" s="3"/>
       <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
-    </row>
-    <row r="118" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA117" s="3"/>
+      <c r="AB117" s="3"/>
+      <c r="AC117" s="3"/>
+      <c r="AD117" s="3"/>
+    </row>
+    <row r="118" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -5371,8 +5974,12 @@
       <c r="X118" s="3"/>
       <c r="Y118" s="3"/>
       <c r="Z118" s="3"/>
-    </row>
-    <row r="119" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA118" s="3"/>
+      <c r="AB118" s="3"/>
+      <c r="AC118" s="3"/>
+      <c r="AD118" s="3"/>
+    </row>
+    <row r="119" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -5397,8 +6004,12 @@
       <c r="X119" s="3"/>
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
-    </row>
-    <row r="120" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA119" s="3"/>
+      <c r="AB119" s="3"/>
+      <c r="AC119" s="3"/>
+      <c r="AD119" s="3"/>
+    </row>
+    <row r="120" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -5423,8 +6034,12 @@
       <c r="X120" s="3"/>
       <c r="Y120" s="3"/>
       <c r="Z120" s="3"/>
-    </row>
-    <row r="121" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA120" s="3"/>
+      <c r="AB120" s="3"/>
+      <c r="AC120" s="3"/>
+      <c r="AD120" s="3"/>
+    </row>
+    <row r="121" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -5449,8 +6064,12 @@
       <c r="X121" s="3"/>
       <c r="Y121" s="3"/>
       <c r="Z121" s="3"/>
-    </row>
-    <row r="122" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA121" s="3"/>
+      <c r="AB121" s="3"/>
+      <c r="AC121" s="3"/>
+      <c r="AD121" s="3"/>
+    </row>
+    <row r="122" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -5475,8 +6094,12 @@
       <c r="X122" s="3"/>
       <c r="Y122" s="3"/>
       <c r="Z122" s="3"/>
-    </row>
-    <row r="123" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA122" s="3"/>
+      <c r="AB122" s="3"/>
+      <c r="AC122" s="3"/>
+      <c r="AD122" s="3"/>
+    </row>
+    <row r="123" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -5501,8 +6124,12 @@
       <c r="X123" s="3"/>
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
-    </row>
-    <row r="124" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA123" s="3"/>
+      <c r="AB123" s="3"/>
+      <c r="AC123" s="3"/>
+      <c r="AD123" s="3"/>
+    </row>
+    <row r="124" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -5527,8 +6154,12 @@
       <c r="X124" s="3"/>
       <c r="Y124" s="3"/>
       <c r="Z124" s="3"/>
-    </row>
-    <row r="125" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA124" s="3"/>
+      <c r="AB124" s="3"/>
+      <c r="AC124" s="3"/>
+      <c r="AD124" s="3"/>
+    </row>
+    <row r="125" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -5553,8 +6184,12 @@
       <c r="X125" s="3"/>
       <c r="Y125" s="3"/>
       <c r="Z125" s="3"/>
-    </row>
-    <row r="126" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA125" s="3"/>
+      <c r="AB125" s="3"/>
+      <c r="AC125" s="3"/>
+      <c r="AD125" s="3"/>
+    </row>
+    <row r="126" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -5579,8 +6214,12 @@
       <c r="X126" s="3"/>
       <c r="Y126" s="3"/>
       <c r="Z126" s="3"/>
-    </row>
-    <row r="127" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA126" s="3"/>
+      <c r="AB126" s="3"/>
+      <c r="AC126" s="3"/>
+      <c r="AD126" s="3"/>
+    </row>
+    <row r="127" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -5605,8 +6244,12 @@
       <c r="X127" s="3"/>
       <c r="Y127" s="3"/>
       <c r="Z127" s="3"/>
-    </row>
-    <row r="128" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA127" s="3"/>
+      <c r="AB127" s="3"/>
+      <c r="AC127" s="3"/>
+      <c r="AD127" s="3"/>
+    </row>
+    <row r="128" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -5631,8 +6274,12 @@
       <c r="X128" s="3"/>
       <c r="Y128" s="3"/>
       <c r="Z128" s="3"/>
-    </row>
-    <row r="129" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA128" s="3"/>
+      <c r="AB128" s="3"/>
+      <c r="AC128" s="3"/>
+      <c r="AD128" s="3"/>
+    </row>
+    <row r="129" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -5657,8 +6304,12 @@
       <c r="X129" s="3"/>
       <c r="Y129" s="3"/>
       <c r="Z129" s="3"/>
-    </row>
-    <row r="130" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA129" s="3"/>
+      <c r="AB129" s="3"/>
+      <c r="AC129" s="3"/>
+      <c r="AD129" s="3"/>
+    </row>
+    <row r="130" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -5683,8 +6334,12 @@
       <c r="X130" s="3"/>
       <c r="Y130" s="3"/>
       <c r="Z130" s="3"/>
-    </row>
-    <row r="131" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA130" s="3"/>
+      <c r="AB130" s="3"/>
+      <c r="AC130" s="3"/>
+      <c r="AD130" s="3"/>
+    </row>
+    <row r="131" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -5709,8 +6364,12 @@
       <c r="X131" s="3"/>
       <c r="Y131" s="3"/>
       <c r="Z131" s="3"/>
-    </row>
-    <row r="132" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA131" s="3"/>
+      <c r="AB131" s="3"/>
+      <c r="AC131" s="3"/>
+      <c r="AD131" s="3"/>
+    </row>
+    <row r="132" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -5735,8 +6394,12 @@
       <c r="X132" s="3"/>
       <c r="Y132" s="3"/>
       <c r="Z132" s="3"/>
-    </row>
-    <row r="133" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA132" s="3"/>
+      <c r="AB132" s="3"/>
+      <c r="AC132" s="3"/>
+      <c r="AD132" s="3"/>
+    </row>
+    <row r="133" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -5761,8 +6424,12 @@
       <c r="X133" s="3"/>
       <c r="Y133" s="3"/>
       <c r="Z133" s="3"/>
-    </row>
-    <row r="134" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA133" s="3"/>
+      <c r="AB133" s="3"/>
+      <c r="AC133" s="3"/>
+      <c r="AD133" s="3"/>
+    </row>
+    <row r="134" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -5787,8 +6454,12 @@
       <c r="X134" s="3"/>
       <c r="Y134" s="3"/>
       <c r="Z134" s="3"/>
-    </row>
-    <row r="135" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA134" s="3"/>
+      <c r="AB134" s="3"/>
+      <c r="AC134" s="3"/>
+      <c r="AD134" s="3"/>
+    </row>
+    <row r="135" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -5813,8 +6484,12 @@
       <c r="X135" s="3"/>
       <c r="Y135" s="3"/>
       <c r="Z135" s="3"/>
-    </row>
-    <row r="136" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA135" s="3"/>
+      <c r="AB135" s="3"/>
+      <c r="AC135" s="3"/>
+      <c r="AD135" s="3"/>
+    </row>
+    <row r="136" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -5839,8 +6514,12 @@
       <c r="X136" s="3"/>
       <c r="Y136" s="3"/>
       <c r="Z136" s="3"/>
-    </row>
-    <row r="137" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA136" s="3"/>
+      <c r="AB136" s="3"/>
+      <c r="AC136" s="3"/>
+      <c r="AD136" s="3"/>
+    </row>
+    <row r="137" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -5865,8 +6544,12 @@
       <c r="X137" s="3"/>
       <c r="Y137" s="3"/>
       <c r="Z137" s="3"/>
-    </row>
-    <row r="138" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA137" s="3"/>
+      <c r="AB137" s="3"/>
+      <c r="AC137" s="3"/>
+      <c r="AD137" s="3"/>
+    </row>
+    <row r="138" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -5891,8 +6574,12 @@
       <c r="X138" s="3"/>
       <c r="Y138" s="3"/>
       <c r="Z138" s="3"/>
-    </row>
-    <row r="139" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA138" s="3"/>
+      <c r="AB138" s="3"/>
+      <c r="AC138" s="3"/>
+      <c r="AD138" s="3"/>
+    </row>
+    <row r="139" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -5917,8 +6604,12 @@
       <c r="X139" s="3"/>
       <c r="Y139" s="3"/>
       <c r="Z139" s="3"/>
-    </row>
-    <row r="140" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA139" s="3"/>
+      <c r="AB139" s="3"/>
+      <c r="AC139" s="3"/>
+      <c r="AD139" s="3"/>
+    </row>
+    <row r="140" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -5943,8 +6634,12 @@
       <c r="X140" s="3"/>
       <c r="Y140" s="3"/>
       <c r="Z140" s="3"/>
-    </row>
-    <row r="141" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA140" s="3"/>
+      <c r="AB140" s="3"/>
+      <c r="AC140" s="3"/>
+      <c r="AD140" s="3"/>
+    </row>
+    <row r="141" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -5969,8 +6664,12 @@
       <c r="X141" s="3"/>
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
-    </row>
-    <row r="142" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA141" s="3"/>
+      <c r="AB141" s="3"/>
+      <c r="AC141" s="3"/>
+      <c r="AD141" s="3"/>
+    </row>
+    <row r="142" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -5995,8 +6694,12 @@
       <c r="X142" s="3"/>
       <c r="Y142" s="3"/>
       <c r="Z142" s="3"/>
-    </row>
-    <row r="143" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA142" s="3"/>
+      <c r="AB142" s="3"/>
+      <c r="AC142" s="3"/>
+      <c r="AD142" s="3"/>
+    </row>
+    <row r="143" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -6021,8 +6724,12 @@
       <c r="X143" s="3"/>
       <c r="Y143" s="3"/>
       <c r="Z143" s="3"/>
-    </row>
-    <row r="144" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA143" s="3"/>
+      <c r="AB143" s="3"/>
+      <c r="AC143" s="3"/>
+      <c r="AD143" s="3"/>
+    </row>
+    <row r="144" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -6047,8 +6754,12 @@
       <c r="X144" s="3"/>
       <c r="Y144" s="3"/>
       <c r="Z144" s="3"/>
-    </row>
-    <row r="145" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA144" s="3"/>
+      <c r="AB144" s="3"/>
+      <c r="AC144" s="3"/>
+      <c r="AD144" s="3"/>
+    </row>
+    <row r="145" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -6073,8 +6784,12 @@
       <c r="X145" s="3"/>
       <c r="Y145" s="3"/>
       <c r="Z145" s="3"/>
-    </row>
-    <row r="146" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA145" s="3"/>
+      <c r="AB145" s="3"/>
+      <c r="AC145" s="3"/>
+      <c r="AD145" s="3"/>
+    </row>
+    <row r="146" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -6099,8 +6814,12 @@
       <c r="X146" s="3"/>
       <c r="Y146" s="3"/>
       <c r="Z146" s="3"/>
-    </row>
-    <row r="147" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA146" s="3"/>
+      <c r="AB146" s="3"/>
+      <c r="AC146" s="3"/>
+      <c r="AD146" s="3"/>
+    </row>
+    <row r="147" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -6125,8 +6844,12 @@
       <c r="X147" s="3"/>
       <c r="Y147" s="3"/>
       <c r="Z147" s="3"/>
-    </row>
-    <row r="148" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA147" s="3"/>
+      <c r="AB147" s="3"/>
+      <c r="AC147" s="3"/>
+      <c r="AD147" s="3"/>
+    </row>
+    <row r="148" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -6151,8 +6874,12 @@
       <c r="X148" s="3"/>
       <c r="Y148" s="3"/>
       <c r="Z148" s="3"/>
-    </row>
-    <row r="149" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA148" s="3"/>
+      <c r="AB148" s="3"/>
+      <c r="AC148" s="3"/>
+      <c r="AD148" s="3"/>
+    </row>
+    <row r="149" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -6177,8 +6904,12 @@
       <c r="X149" s="3"/>
       <c r="Y149" s="3"/>
       <c r="Z149" s="3"/>
-    </row>
-    <row r="150" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA149" s="3"/>
+      <c r="AB149" s="3"/>
+      <c r="AC149" s="3"/>
+      <c r="AD149" s="3"/>
+    </row>
+    <row r="150" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -6203,8 +6934,12 @@
       <c r="X150" s="3"/>
       <c r="Y150" s="3"/>
       <c r="Z150" s="3"/>
-    </row>
-    <row r="151" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA150" s="3"/>
+      <c r="AB150" s="3"/>
+      <c r="AC150" s="3"/>
+      <c r="AD150" s="3"/>
+    </row>
+    <row r="151" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -6229,8 +6964,12 @@
       <c r="X151" s="3"/>
       <c r="Y151" s="3"/>
       <c r="Z151" s="3"/>
-    </row>
-    <row r="152" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA151" s="3"/>
+      <c r="AB151" s="3"/>
+      <c r="AC151" s="3"/>
+      <c r="AD151" s="3"/>
+    </row>
+    <row r="152" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -6255,8 +6994,12 @@
       <c r="X152" s="3"/>
       <c r="Y152" s="3"/>
       <c r="Z152" s="3"/>
-    </row>
-    <row r="153" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA152" s="3"/>
+      <c r="AB152" s="3"/>
+      <c r="AC152" s="3"/>
+      <c r="AD152" s="3"/>
+    </row>
+    <row r="153" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -6281,8 +7024,12 @@
       <c r="X153" s="3"/>
       <c r="Y153" s="3"/>
       <c r="Z153" s="3"/>
-    </row>
-    <row r="154" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA153" s="3"/>
+      <c r="AB153" s="3"/>
+      <c r="AC153" s="3"/>
+      <c r="AD153" s="3"/>
+    </row>
+    <row r="154" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -6307,8 +7054,12 @@
       <c r="X154" s="3"/>
       <c r="Y154" s="3"/>
       <c r="Z154" s="3"/>
-    </row>
-    <row r="155" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA154" s="3"/>
+      <c r="AB154" s="3"/>
+      <c r="AC154" s="3"/>
+      <c r="AD154" s="3"/>
+    </row>
+    <row r="155" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -6333,8 +7084,12 @@
       <c r="X155" s="3"/>
       <c r="Y155" s="3"/>
       <c r="Z155" s="3"/>
-    </row>
-    <row r="156" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA155" s="3"/>
+      <c r="AB155" s="3"/>
+      <c r="AC155" s="3"/>
+      <c r="AD155" s="3"/>
+    </row>
+    <row r="156" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -6359,8 +7114,12 @@
       <c r="X156" s="3"/>
       <c r="Y156" s="3"/>
       <c r="Z156" s="3"/>
-    </row>
-    <row r="157" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA156" s="3"/>
+      <c r="AB156" s="3"/>
+      <c r="AC156" s="3"/>
+      <c r="AD156" s="3"/>
+    </row>
+    <row r="157" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -6385,8 +7144,12 @@
       <c r="X157" s="3"/>
       <c r="Y157" s="3"/>
       <c r="Z157" s="3"/>
-    </row>
-    <row r="158" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA157" s="3"/>
+      <c r="AB157" s="3"/>
+      <c r="AC157" s="3"/>
+      <c r="AD157" s="3"/>
+    </row>
+    <row r="158" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -6411,8 +7174,12 @@
       <c r="X158" s="3"/>
       <c r="Y158" s="3"/>
       <c r="Z158" s="3"/>
-    </row>
-    <row r="159" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA158" s="3"/>
+      <c r="AB158" s="3"/>
+      <c r="AC158" s="3"/>
+      <c r="AD158" s="3"/>
+    </row>
+    <row r="159" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -6437,8 +7204,12 @@
       <c r="X159" s="3"/>
       <c r="Y159" s="3"/>
       <c r="Z159" s="3"/>
-    </row>
-    <row r="160" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA159" s="3"/>
+      <c r="AB159" s="3"/>
+      <c r="AC159" s="3"/>
+      <c r="AD159" s="3"/>
+    </row>
+    <row r="160" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -6463,8 +7234,12 @@
       <c r="X160" s="3"/>
       <c r="Y160" s="3"/>
       <c r="Z160" s="3"/>
-    </row>
-    <row r="161" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA160" s="3"/>
+      <c r="AB160" s="3"/>
+      <c r="AC160" s="3"/>
+      <c r="AD160" s="3"/>
+    </row>
+    <row r="161" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -6489,8 +7264,12 @@
       <c r="X161" s="3"/>
       <c r="Y161" s="3"/>
       <c r="Z161" s="3"/>
-    </row>
-    <row r="162" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA161" s="3"/>
+      <c r="AB161" s="3"/>
+      <c r="AC161" s="3"/>
+      <c r="AD161" s="3"/>
+    </row>
+    <row r="162" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -6515,8 +7294,12 @@
       <c r="X162" s="3"/>
       <c r="Y162" s="3"/>
       <c r="Z162" s="3"/>
-    </row>
-    <row r="163" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA162" s="3"/>
+      <c r="AB162" s="3"/>
+      <c r="AC162" s="3"/>
+      <c r="AD162" s="3"/>
+    </row>
+    <row r="163" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -6541,8 +7324,12 @@
       <c r="X163" s="3"/>
       <c r="Y163" s="3"/>
       <c r="Z163" s="3"/>
-    </row>
-    <row r="164" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA163" s="3"/>
+      <c r="AB163" s="3"/>
+      <c r="AC163" s="3"/>
+      <c r="AD163" s="3"/>
+    </row>
+    <row r="164" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -6567,8 +7354,12 @@
       <c r="X164" s="3"/>
       <c r="Y164" s="3"/>
       <c r="Z164" s="3"/>
-    </row>
-    <row r="165" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA164" s="3"/>
+      <c r="AB164" s="3"/>
+      <c r="AC164" s="3"/>
+      <c r="AD164" s="3"/>
+    </row>
+    <row r="165" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -6593,8 +7384,12 @@
       <c r="X165" s="3"/>
       <c r="Y165" s="3"/>
       <c r="Z165" s="3"/>
-    </row>
-    <row r="166" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA165" s="3"/>
+      <c r="AB165" s="3"/>
+      <c r="AC165" s="3"/>
+      <c r="AD165" s="3"/>
+    </row>
+    <row r="166" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -6619,8 +7414,12 @@
       <c r="X166" s="3"/>
       <c r="Y166" s="3"/>
       <c r="Z166" s="3"/>
-    </row>
-    <row r="167" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA166" s="3"/>
+      <c r="AB166" s="3"/>
+      <c r="AC166" s="3"/>
+      <c r="AD166" s="3"/>
+    </row>
+    <row r="167" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -6645,8 +7444,12 @@
       <c r="X167" s="3"/>
       <c r="Y167" s="3"/>
       <c r="Z167" s="3"/>
-    </row>
-    <row r="168" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA167" s="3"/>
+      <c r="AB167" s="3"/>
+      <c r="AC167" s="3"/>
+      <c r="AD167" s="3"/>
+    </row>
+    <row r="168" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -6671,8 +7474,12 @@
       <c r="X168" s="3"/>
       <c r="Y168" s="3"/>
       <c r="Z168" s="3"/>
-    </row>
-    <row r="169" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA168" s="3"/>
+      <c r="AB168" s="3"/>
+      <c r="AC168" s="3"/>
+      <c r="AD168" s="3"/>
+    </row>
+    <row r="169" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -6697,8 +7504,12 @@
       <c r="X169" s="3"/>
       <c r="Y169" s="3"/>
       <c r="Z169" s="3"/>
-    </row>
-    <row r="170" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA169" s="3"/>
+      <c r="AB169" s="3"/>
+      <c r="AC169" s="3"/>
+      <c r="AD169" s="3"/>
+    </row>
+    <row r="170" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -6723,8 +7534,12 @@
       <c r="X170" s="3"/>
       <c r="Y170" s="3"/>
       <c r="Z170" s="3"/>
-    </row>
-    <row r="171" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA170" s="3"/>
+      <c r="AB170" s="3"/>
+      <c r="AC170" s="3"/>
+      <c r="AD170" s="3"/>
+    </row>
+    <row r="171" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -6749,8 +7564,12 @@
       <c r="X171" s="3"/>
       <c r="Y171" s="3"/>
       <c r="Z171" s="3"/>
-    </row>
-    <row r="172" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA171" s="3"/>
+      <c r="AB171" s="3"/>
+      <c r="AC171" s="3"/>
+      <c r="AD171" s="3"/>
+    </row>
+    <row r="172" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -6775,8 +7594,12 @@
       <c r="X172" s="3"/>
       <c r="Y172" s="3"/>
       <c r="Z172" s="3"/>
-    </row>
-    <row r="173" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA172" s="3"/>
+      <c r="AB172" s="3"/>
+      <c r="AC172" s="3"/>
+      <c r="AD172" s="3"/>
+    </row>
+    <row r="173" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -6801,8 +7624,12 @@
       <c r="X173" s="3"/>
       <c r="Y173" s="3"/>
       <c r="Z173" s="3"/>
-    </row>
-    <row r="174" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA173" s="3"/>
+      <c r="AB173" s="3"/>
+      <c r="AC173" s="3"/>
+      <c r="AD173" s="3"/>
+    </row>
+    <row r="174" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -6827,8 +7654,12 @@
       <c r="X174" s="3"/>
       <c r="Y174" s="3"/>
       <c r="Z174" s="3"/>
-    </row>
-    <row r="175" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA174" s="3"/>
+      <c r="AB174" s="3"/>
+      <c r="AC174" s="3"/>
+      <c r="AD174" s="3"/>
+    </row>
+    <row r="175" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -6853,8 +7684,12 @@
       <c r="X175" s="3"/>
       <c r="Y175" s="3"/>
       <c r="Z175" s="3"/>
-    </row>
-    <row r="176" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA175" s="3"/>
+      <c r="AB175" s="3"/>
+      <c r="AC175" s="3"/>
+      <c r="AD175" s="3"/>
+    </row>
+    <row r="176" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -6879,8 +7714,12 @@
       <c r="X176" s="3"/>
       <c r="Y176" s="3"/>
       <c r="Z176" s="3"/>
-    </row>
-    <row r="177" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA176" s="3"/>
+      <c r="AB176" s="3"/>
+      <c r="AC176" s="3"/>
+      <c r="AD176" s="3"/>
+    </row>
+    <row r="177" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -6905,8 +7744,12 @@
       <c r="X177" s="3"/>
       <c r="Y177" s="3"/>
       <c r="Z177" s="3"/>
-    </row>
-    <row r="178" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA177" s="3"/>
+      <c r="AB177" s="3"/>
+      <c r="AC177" s="3"/>
+      <c r="AD177" s="3"/>
+    </row>
+    <row r="178" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -6931,8 +7774,12 @@
       <c r="X178" s="3"/>
       <c r="Y178" s="3"/>
       <c r="Z178" s="3"/>
-    </row>
-    <row r="179" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA178" s="3"/>
+      <c r="AB178" s="3"/>
+      <c r="AC178" s="3"/>
+      <c r="AD178" s="3"/>
+    </row>
+    <row r="179" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -6957,8 +7804,12 @@
       <c r="X179" s="3"/>
       <c r="Y179" s="3"/>
       <c r="Z179" s="3"/>
-    </row>
-    <row r="180" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA179" s="3"/>
+      <c r="AB179" s="3"/>
+      <c r="AC179" s="3"/>
+      <c r="AD179" s="3"/>
+    </row>
+    <row r="180" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -6983,8 +7834,12 @@
       <c r="X180" s="3"/>
       <c r="Y180" s="3"/>
       <c r="Z180" s="3"/>
-    </row>
-    <row r="181" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA180" s="3"/>
+      <c r="AB180" s="3"/>
+      <c r="AC180" s="3"/>
+      <c r="AD180" s="3"/>
+    </row>
+    <row r="181" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -7009,8 +7864,12 @@
       <c r="X181" s="3"/>
       <c r="Y181" s="3"/>
       <c r="Z181" s="3"/>
-    </row>
-    <row r="182" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA181" s="3"/>
+      <c r="AB181" s="3"/>
+      <c r="AC181" s="3"/>
+      <c r="AD181" s="3"/>
+    </row>
+    <row r="182" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -7035,8 +7894,12 @@
       <c r="X182" s="3"/>
       <c r="Y182" s="3"/>
       <c r="Z182" s="3"/>
-    </row>
-    <row r="183" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA182" s="3"/>
+      <c r="AB182" s="3"/>
+      <c r="AC182" s="3"/>
+      <c r="AD182" s="3"/>
+    </row>
+    <row r="183" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -7061,8 +7924,12 @@
       <c r="X183" s="3"/>
       <c r="Y183" s="3"/>
       <c r="Z183" s="3"/>
-    </row>
-    <row r="184" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA183" s="3"/>
+      <c r="AB183" s="3"/>
+      <c r="AC183" s="3"/>
+      <c r="AD183" s="3"/>
+    </row>
+    <row r="184" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -7087,8 +7954,12 @@
       <c r="X184" s="3"/>
       <c r="Y184" s="3"/>
       <c r="Z184" s="3"/>
-    </row>
-    <row r="185" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA184" s="3"/>
+      <c r="AB184" s="3"/>
+      <c r="AC184" s="3"/>
+      <c r="AD184" s="3"/>
+    </row>
+    <row r="185" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -7113,8 +7984,12 @@
       <c r="X185" s="3"/>
       <c r="Y185" s="3"/>
       <c r="Z185" s="3"/>
-    </row>
-    <row r="186" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA185" s="3"/>
+      <c r="AB185" s="3"/>
+      <c r="AC185" s="3"/>
+      <c r="AD185" s="3"/>
+    </row>
+    <row r="186" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -7139,8 +8014,12 @@
       <c r="X186" s="3"/>
       <c r="Y186" s="3"/>
       <c r="Z186" s="3"/>
-    </row>
-    <row r="187" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA186" s="3"/>
+      <c r="AB186" s="3"/>
+      <c r="AC186" s="3"/>
+      <c r="AD186" s="3"/>
+    </row>
+    <row r="187" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -7165,8 +8044,12 @@
       <c r="X187" s="3"/>
       <c r="Y187" s="3"/>
       <c r="Z187" s="3"/>
-    </row>
-    <row r="188" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA187" s="3"/>
+      <c r="AB187" s="3"/>
+      <c r="AC187" s="3"/>
+      <c r="AD187" s="3"/>
+    </row>
+    <row r="188" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -7191,8 +8074,12 @@
       <c r="X188" s="3"/>
       <c r="Y188" s="3"/>
       <c r="Z188" s="3"/>
-    </row>
-    <row r="189" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA188" s="3"/>
+      <c r="AB188" s="3"/>
+      <c r="AC188" s="3"/>
+      <c r="AD188" s="3"/>
+    </row>
+    <row r="189" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -7217,8 +8104,12 @@
       <c r="X189" s="3"/>
       <c r="Y189" s="3"/>
       <c r="Z189" s="3"/>
-    </row>
-    <row r="190" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA189" s="3"/>
+      <c r="AB189" s="3"/>
+      <c r="AC189" s="3"/>
+      <c r="AD189" s="3"/>
+    </row>
+    <row r="190" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -7243,8 +8134,12 @@
       <c r="X190" s="3"/>
       <c r="Y190" s="3"/>
       <c r="Z190" s="3"/>
-    </row>
-    <row r="191" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA190" s="3"/>
+      <c r="AB190" s="3"/>
+      <c r="AC190" s="3"/>
+      <c r="AD190" s="3"/>
+    </row>
+    <row r="191" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -7269,8 +8164,12 @@
       <c r="X191" s="3"/>
       <c r="Y191" s="3"/>
       <c r="Z191" s="3"/>
-    </row>
-    <row r="192" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA191" s="3"/>
+      <c r="AB191" s="3"/>
+      <c r="AC191" s="3"/>
+      <c r="AD191" s="3"/>
+    </row>
+    <row r="192" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -7295,8 +8194,12 @@
       <c r="X192" s="3"/>
       <c r="Y192" s="3"/>
       <c r="Z192" s="3"/>
-    </row>
-    <row r="193" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA192" s="3"/>
+      <c r="AB192" s="3"/>
+      <c r="AC192" s="3"/>
+      <c r="AD192" s="3"/>
+    </row>
+    <row r="193" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -7321,8 +8224,12 @@
       <c r="X193" s="3"/>
       <c r="Y193" s="3"/>
       <c r="Z193" s="3"/>
-    </row>
-    <row r="194" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA193" s="3"/>
+      <c r="AB193" s="3"/>
+      <c r="AC193" s="3"/>
+      <c r="AD193" s="3"/>
+    </row>
+    <row r="194" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -7347,8 +8254,12 @@
       <c r="X194" s="3"/>
       <c r="Y194" s="3"/>
       <c r="Z194" s="3"/>
-    </row>
-    <row r="195" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA194" s="3"/>
+      <c r="AB194" s="3"/>
+      <c r="AC194" s="3"/>
+      <c r="AD194" s="3"/>
+    </row>
+    <row r="195" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -7373,8 +8284,12 @@
       <c r="X195" s="3"/>
       <c r="Y195" s="3"/>
       <c r="Z195" s="3"/>
-    </row>
-    <row r="196" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA195" s="3"/>
+      <c r="AB195" s="3"/>
+      <c r="AC195" s="3"/>
+      <c r="AD195" s="3"/>
+    </row>
+    <row r="196" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -7399,8 +8314,12 @@
       <c r="X196" s="3"/>
       <c r="Y196" s="3"/>
       <c r="Z196" s="3"/>
-    </row>
-    <row r="197" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA196" s="3"/>
+      <c r="AB196" s="3"/>
+      <c r="AC196" s="3"/>
+      <c r="AD196" s="3"/>
+    </row>
+    <row r="197" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -7425,8 +8344,12 @@
       <c r="X197" s="3"/>
       <c r="Y197" s="3"/>
       <c r="Z197" s="3"/>
-    </row>
-    <row r="198" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA197" s="3"/>
+      <c r="AB197" s="3"/>
+      <c r="AC197" s="3"/>
+      <c r="AD197" s="3"/>
+    </row>
+    <row r="198" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -7451,8 +8374,12 @@
       <c r="X198" s="3"/>
       <c r="Y198" s="3"/>
       <c r="Z198" s="3"/>
-    </row>
-    <row r="199" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA198" s="3"/>
+      <c r="AB198" s="3"/>
+      <c r="AC198" s="3"/>
+      <c r="AD198" s="3"/>
+    </row>
+    <row r="199" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -7477,8 +8404,12 @@
       <c r="X199" s="3"/>
       <c r="Y199" s="3"/>
       <c r="Z199" s="3"/>
-    </row>
-    <row r="200" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA199" s="3"/>
+      <c r="AB199" s="3"/>
+      <c r="AC199" s="3"/>
+      <c r="AD199" s="3"/>
+    </row>
+    <row r="200" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -7503,8 +8434,12 @@
       <c r="X200" s="3"/>
       <c r="Y200" s="3"/>
       <c r="Z200" s="3"/>
-    </row>
-    <row r="201" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA200" s="3"/>
+      <c r="AB200" s="3"/>
+      <c r="AC200" s="3"/>
+      <c r="AD200" s="3"/>
+    </row>
+    <row r="201" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -7529,8 +8464,12 @@
       <c r="X201" s="3"/>
       <c r="Y201" s="3"/>
       <c r="Z201" s="3"/>
-    </row>
-    <row r="202" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA201" s="3"/>
+      <c r="AB201" s="3"/>
+      <c r="AC201" s="3"/>
+      <c r="AD201" s="3"/>
+    </row>
+    <row r="202" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -7555,8 +8494,12 @@
       <c r="X202" s="3"/>
       <c r="Y202" s="3"/>
       <c r="Z202" s="3"/>
-    </row>
-    <row r="203" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA202" s="3"/>
+      <c r="AB202" s="3"/>
+      <c r="AC202" s="3"/>
+      <c r="AD202" s="3"/>
+    </row>
+    <row r="203" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -7581,8 +8524,12 @@
       <c r="X203" s="3"/>
       <c r="Y203" s="3"/>
       <c r="Z203" s="3"/>
-    </row>
-    <row r="204" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA203" s="3"/>
+      <c r="AB203" s="3"/>
+      <c r="AC203" s="3"/>
+      <c r="AD203" s="3"/>
+    </row>
+    <row r="204" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -7607,8 +8554,12 @@
       <c r="X204" s="3"/>
       <c r="Y204" s="3"/>
       <c r="Z204" s="3"/>
-    </row>
-    <row r="205" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA204" s="3"/>
+      <c r="AB204" s="3"/>
+      <c r="AC204" s="3"/>
+      <c r="AD204" s="3"/>
+    </row>
+    <row r="205" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -7633,8 +8584,12 @@
       <c r="X205" s="3"/>
       <c r="Y205" s="3"/>
       <c r="Z205" s="3"/>
-    </row>
-    <row r="206" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA205" s="3"/>
+      <c r="AB205" s="3"/>
+      <c r="AC205" s="3"/>
+      <c r="AD205" s="3"/>
+    </row>
+    <row r="206" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -7659,8 +8614,12 @@
       <c r="X206" s="3"/>
       <c r="Y206" s="3"/>
       <c r="Z206" s="3"/>
-    </row>
-    <row r="207" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA206" s="3"/>
+      <c r="AB206" s="3"/>
+      <c r="AC206" s="3"/>
+      <c r="AD206" s="3"/>
+    </row>
+    <row r="207" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -7685,8 +8644,12 @@
       <c r="X207" s="3"/>
       <c r="Y207" s="3"/>
       <c r="Z207" s="3"/>
-    </row>
-    <row r="208" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA207" s="3"/>
+      <c r="AB207" s="3"/>
+      <c r="AC207" s="3"/>
+      <c r="AD207" s="3"/>
+    </row>
+    <row r="208" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -7711,8 +8674,12 @@
       <c r="X208" s="3"/>
       <c r="Y208" s="3"/>
       <c r="Z208" s="3"/>
-    </row>
-    <row r="209" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA208" s="3"/>
+      <c r="AB208" s="3"/>
+      <c r="AC208" s="3"/>
+      <c r="AD208" s="3"/>
+    </row>
+    <row r="209" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -7737,8 +8704,12 @@
       <c r="X209" s="3"/>
       <c r="Y209" s="3"/>
       <c r="Z209" s="3"/>
-    </row>
-    <row r="210" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA209" s="3"/>
+      <c r="AB209" s="3"/>
+      <c r="AC209" s="3"/>
+      <c r="AD209" s="3"/>
+    </row>
+    <row r="210" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -7763,8 +8734,12 @@
       <c r="X210" s="3"/>
       <c r="Y210" s="3"/>
       <c r="Z210" s="3"/>
-    </row>
-    <row r="211" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA210" s="3"/>
+      <c r="AB210" s="3"/>
+      <c r="AC210" s="3"/>
+      <c r="AD210" s="3"/>
+    </row>
+    <row r="211" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -7789,8 +8764,12 @@
       <c r="X211" s="3"/>
       <c r="Y211" s="3"/>
       <c r="Z211" s="3"/>
-    </row>
-    <row r="212" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA211" s="3"/>
+      <c r="AB211" s="3"/>
+      <c r="AC211" s="3"/>
+      <c r="AD211" s="3"/>
+    </row>
+    <row r="212" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -7815,8 +8794,12 @@
       <c r="X212" s="3"/>
       <c r="Y212" s="3"/>
       <c r="Z212" s="3"/>
-    </row>
-    <row r="213" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA212" s="3"/>
+      <c r="AB212" s="3"/>
+      <c r="AC212" s="3"/>
+      <c r="AD212" s="3"/>
+    </row>
+    <row r="213" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -7841,8 +8824,12 @@
       <c r="X213" s="3"/>
       <c r="Y213" s="3"/>
       <c r="Z213" s="3"/>
-    </row>
-    <row r="214" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA213" s="3"/>
+      <c r="AB213" s="3"/>
+      <c r="AC213" s="3"/>
+      <c r="AD213" s="3"/>
+    </row>
+    <row r="214" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -7867,8 +8854,12 @@
       <c r="X214" s="3"/>
       <c r="Y214" s="3"/>
       <c r="Z214" s="3"/>
-    </row>
-    <row r="215" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA214" s="3"/>
+      <c r="AB214" s="3"/>
+      <c r="AC214" s="3"/>
+      <c r="AD214" s="3"/>
+    </row>
+    <row r="215" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -7893,8 +8884,12 @@
       <c r="X215" s="3"/>
       <c r="Y215" s="3"/>
       <c r="Z215" s="3"/>
-    </row>
-    <row r="216" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA215" s="3"/>
+      <c r="AB215" s="3"/>
+      <c r="AC215" s="3"/>
+      <c r="AD215" s="3"/>
+    </row>
+    <row r="216" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -7919,8 +8914,12 @@
       <c r="X216" s="3"/>
       <c r="Y216" s="3"/>
       <c r="Z216" s="3"/>
-    </row>
-    <row r="217" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA216" s="3"/>
+      <c r="AB216" s="3"/>
+      <c r="AC216" s="3"/>
+      <c r="AD216" s="3"/>
+    </row>
+    <row r="217" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -7945,8 +8944,12 @@
       <c r="X217" s="3"/>
       <c r="Y217" s="3"/>
       <c r="Z217" s="3"/>
-    </row>
-    <row r="218" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA217" s="3"/>
+      <c r="AB217" s="3"/>
+      <c r="AC217" s="3"/>
+      <c r="AD217" s="3"/>
+    </row>
+    <row r="218" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -7971,8 +8974,12 @@
       <c r="X218" s="3"/>
       <c r="Y218" s="3"/>
       <c r="Z218" s="3"/>
-    </row>
-    <row r="219" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA218" s="3"/>
+      <c r="AB218" s="3"/>
+      <c r="AC218" s="3"/>
+      <c r="AD218" s="3"/>
+    </row>
+    <row r="219" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -7997,8 +9004,12 @@
       <c r="X219" s="3"/>
       <c r="Y219" s="3"/>
       <c r="Z219" s="3"/>
-    </row>
-    <row r="220" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA219" s="3"/>
+      <c r="AB219" s="3"/>
+      <c r="AC219" s="3"/>
+      <c r="AD219" s="3"/>
+    </row>
+    <row r="220" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -8023,8 +9034,12 @@
       <c r="X220" s="3"/>
       <c r="Y220" s="3"/>
       <c r="Z220" s="3"/>
-    </row>
-    <row r="221" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA220" s="3"/>
+      <c r="AB220" s="3"/>
+      <c r="AC220" s="3"/>
+      <c r="AD220" s="3"/>
+    </row>
+    <row r="221" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -8049,8 +9064,12 @@
       <c r="X221" s="3"/>
       <c r="Y221" s="3"/>
       <c r="Z221" s="3"/>
-    </row>
-    <row r="222" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA221" s="3"/>
+      <c r="AB221" s="3"/>
+      <c r="AC221" s="3"/>
+      <c r="AD221" s="3"/>
+    </row>
+    <row r="222" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -8075,8 +9094,12 @@
       <c r="X222" s="3"/>
       <c r="Y222" s="3"/>
       <c r="Z222" s="3"/>
-    </row>
-    <row r="223" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA222" s="3"/>
+      <c r="AB222" s="3"/>
+      <c r="AC222" s="3"/>
+      <c r="AD222" s="3"/>
+    </row>
+    <row r="223" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -8101,8 +9124,12 @@
       <c r="X223" s="3"/>
       <c r="Y223" s="3"/>
       <c r="Z223" s="3"/>
-    </row>
-    <row r="224" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA223" s="3"/>
+      <c r="AB223" s="3"/>
+      <c r="AC223" s="3"/>
+      <c r="AD223" s="3"/>
+    </row>
+    <row r="224" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -8127,8 +9154,12 @@
       <c r="X224" s="3"/>
       <c r="Y224" s="3"/>
       <c r="Z224" s="3"/>
-    </row>
-    <row r="225" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA224" s="3"/>
+      <c r="AB224" s="3"/>
+      <c r="AC224" s="3"/>
+      <c r="AD224" s="3"/>
+    </row>
+    <row r="225" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -8153,8 +9184,12 @@
       <c r="X225" s="3"/>
       <c r="Y225" s="3"/>
       <c r="Z225" s="3"/>
-    </row>
-    <row r="226" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA225" s="3"/>
+      <c r="AB225" s="3"/>
+      <c r="AC225" s="3"/>
+      <c r="AD225" s="3"/>
+    </row>
+    <row r="226" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -8179,8 +9214,12 @@
       <c r="X226" s="3"/>
       <c r="Y226" s="3"/>
       <c r="Z226" s="3"/>
-    </row>
-    <row r="227" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA226" s="3"/>
+      <c r="AB226" s="3"/>
+      <c r="AC226" s="3"/>
+      <c r="AD226" s="3"/>
+    </row>
+    <row r="227" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -8205,8 +9244,12 @@
       <c r="X227" s="3"/>
       <c r="Y227" s="3"/>
       <c r="Z227" s="3"/>
-    </row>
-    <row r="228" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA227" s="3"/>
+      <c r="AB227" s="3"/>
+      <c r="AC227" s="3"/>
+      <c r="AD227" s="3"/>
+    </row>
+    <row r="228" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -8231,8 +9274,12 @@
       <c r="X228" s="3"/>
       <c r="Y228" s="3"/>
       <c r="Z228" s="3"/>
-    </row>
-    <row r="229" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA228" s="3"/>
+      <c r="AB228" s="3"/>
+      <c r="AC228" s="3"/>
+      <c r="AD228" s="3"/>
+    </row>
+    <row r="229" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -8257,8 +9304,12 @@
       <c r="X229" s="3"/>
       <c r="Y229" s="3"/>
       <c r="Z229" s="3"/>
-    </row>
-    <row r="230" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA229" s="3"/>
+      <c r="AB229" s="3"/>
+      <c r="AC229" s="3"/>
+      <c r="AD229" s="3"/>
+    </row>
+    <row r="230" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -8283,8 +9334,12 @@
       <c r="X230" s="3"/>
       <c r="Y230" s="3"/>
       <c r="Z230" s="3"/>
-    </row>
-    <row r="231" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA230" s="3"/>
+      <c r="AB230" s="3"/>
+      <c r="AC230" s="3"/>
+      <c r="AD230" s="3"/>
+    </row>
+    <row r="231" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -8309,8 +9364,12 @@
       <c r="X231" s="3"/>
       <c r="Y231" s="3"/>
       <c r="Z231" s="3"/>
-    </row>
-    <row r="232" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA231" s="3"/>
+      <c r="AB231" s="3"/>
+      <c r="AC231" s="3"/>
+      <c r="AD231" s="3"/>
+    </row>
+    <row r="232" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -8335,8 +9394,12 @@
       <c r="X232" s="3"/>
       <c r="Y232" s="3"/>
       <c r="Z232" s="3"/>
-    </row>
-    <row r="233" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA232" s="3"/>
+      <c r="AB232" s="3"/>
+      <c r="AC232" s="3"/>
+      <c r="AD232" s="3"/>
+    </row>
+    <row r="233" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -8361,8 +9424,12 @@
       <c r="X233" s="3"/>
       <c r="Y233" s="3"/>
       <c r="Z233" s="3"/>
-    </row>
-    <row r="234" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA233" s="3"/>
+      <c r="AB233" s="3"/>
+      <c r="AC233" s="3"/>
+      <c r="AD233" s="3"/>
+    </row>
+    <row r="234" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -8387,8 +9454,12 @@
       <c r="X234" s="3"/>
       <c r="Y234" s="3"/>
       <c r="Z234" s="3"/>
-    </row>
-    <row r="235" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA234" s="3"/>
+      <c r="AB234" s="3"/>
+      <c r="AC234" s="3"/>
+      <c r="AD234" s="3"/>
+    </row>
+    <row r="235" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -8413,8 +9484,12 @@
       <c r="X235" s="3"/>
       <c r="Y235" s="3"/>
       <c r="Z235" s="3"/>
-    </row>
-    <row r="236" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA235" s="3"/>
+      <c r="AB235" s="3"/>
+      <c r="AC235" s="3"/>
+      <c r="AD235" s="3"/>
+    </row>
+    <row r="236" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -8439,8 +9514,12 @@
       <c r="X236" s="3"/>
       <c r="Y236" s="3"/>
       <c r="Z236" s="3"/>
-    </row>
-    <row r="237" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA236" s="3"/>
+      <c r="AB236" s="3"/>
+      <c r="AC236" s="3"/>
+      <c r="AD236" s="3"/>
+    </row>
+    <row r="237" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -8465,8 +9544,12 @@
       <c r="X237" s="3"/>
       <c r="Y237" s="3"/>
       <c r="Z237" s="3"/>
-    </row>
-    <row r="238" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA237" s="3"/>
+      <c r="AB237" s="3"/>
+      <c r="AC237" s="3"/>
+      <c r="AD237" s="3"/>
+    </row>
+    <row r="238" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -8491,8 +9574,12 @@
       <c r="X238" s="3"/>
       <c r="Y238" s="3"/>
       <c r="Z238" s="3"/>
-    </row>
-    <row r="239" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA238" s="3"/>
+      <c r="AB238" s="3"/>
+      <c r="AC238" s="3"/>
+      <c r="AD238" s="3"/>
+    </row>
+    <row r="239" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -8517,8 +9604,12 @@
       <c r="X239" s="3"/>
       <c r="Y239" s="3"/>
       <c r="Z239" s="3"/>
-    </row>
-    <row r="240" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA239" s="3"/>
+      <c r="AB239" s="3"/>
+      <c r="AC239" s="3"/>
+      <c r="AD239" s="3"/>
+    </row>
+    <row r="240" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -8543,8 +9634,12 @@
       <c r="X240" s="3"/>
       <c r="Y240" s="3"/>
       <c r="Z240" s="3"/>
-    </row>
-    <row r="241" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA240" s="3"/>
+      <c r="AB240" s="3"/>
+      <c r="AC240" s="3"/>
+      <c r="AD240" s="3"/>
+    </row>
+    <row r="241" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -8569,8 +9664,12 @@
       <c r="X241" s="3"/>
       <c r="Y241" s="3"/>
       <c r="Z241" s="3"/>
-    </row>
-    <row r="242" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA241" s="3"/>
+      <c r="AB241" s="3"/>
+      <c r="AC241" s="3"/>
+      <c r="AD241" s="3"/>
+    </row>
+    <row r="242" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -8595,8 +9694,12 @@
       <c r="X242" s="3"/>
       <c r="Y242" s="3"/>
       <c r="Z242" s="3"/>
-    </row>
-    <row r="243" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA242" s="3"/>
+      <c r="AB242" s="3"/>
+      <c r="AC242" s="3"/>
+      <c r="AD242" s="3"/>
+    </row>
+    <row r="243" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -8621,8 +9724,12 @@
       <c r="X243" s="3"/>
       <c r="Y243" s="3"/>
       <c r="Z243" s="3"/>
-    </row>
-    <row r="244" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA243" s="3"/>
+      <c r="AB243" s="3"/>
+      <c r="AC243" s="3"/>
+      <c r="AD243" s="3"/>
+    </row>
+    <row r="244" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -8647,8 +9754,12 @@
       <c r="X244" s="3"/>
       <c r="Y244" s="3"/>
       <c r="Z244" s="3"/>
-    </row>
-    <row r="245" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA244" s="3"/>
+      <c r="AB244" s="3"/>
+      <c r="AC244" s="3"/>
+      <c r="AD244" s="3"/>
+    </row>
+    <row r="245" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -8673,8 +9784,12 @@
       <c r="X245" s="3"/>
       <c r="Y245" s="3"/>
       <c r="Z245" s="3"/>
-    </row>
-    <row r="246" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA245" s="3"/>
+      <c r="AB245" s="3"/>
+      <c r="AC245" s="3"/>
+      <c r="AD245" s="3"/>
+    </row>
+    <row r="246" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -8699,8 +9814,12 @@
       <c r="X246" s="3"/>
       <c r="Y246" s="3"/>
       <c r="Z246" s="3"/>
-    </row>
-    <row r="247" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA246" s="3"/>
+      <c r="AB246" s="3"/>
+      <c r="AC246" s="3"/>
+      <c r="AD246" s="3"/>
+    </row>
+    <row r="247" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -8725,8 +9844,12 @@
       <c r="X247" s="3"/>
       <c r="Y247" s="3"/>
       <c r="Z247" s="3"/>
-    </row>
-    <row r="248" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA247" s="3"/>
+      <c r="AB247" s="3"/>
+      <c r="AC247" s="3"/>
+      <c r="AD247" s="3"/>
+    </row>
+    <row r="248" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -8751,8 +9874,12 @@
       <c r="X248" s="3"/>
       <c r="Y248" s="3"/>
       <c r="Z248" s="3"/>
-    </row>
-    <row r="249" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA248" s="3"/>
+      <c r="AB248" s="3"/>
+      <c r="AC248" s="3"/>
+      <c r="AD248" s="3"/>
+    </row>
+    <row r="249" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -8777,8 +9904,12 @@
       <c r="X249" s="3"/>
       <c r="Y249" s="3"/>
       <c r="Z249" s="3"/>
-    </row>
-    <row r="250" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA249" s="3"/>
+      <c r="AB249" s="3"/>
+      <c r="AC249" s="3"/>
+      <c r="AD249" s="3"/>
+    </row>
+    <row r="250" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -8803,8 +9934,12 @@
       <c r="X250" s="3"/>
       <c r="Y250" s="3"/>
       <c r="Z250" s="3"/>
-    </row>
-    <row r="251" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA250" s="3"/>
+      <c r="AB250" s="3"/>
+      <c r="AC250" s="3"/>
+      <c r="AD250" s="3"/>
+    </row>
+    <row r="251" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -8829,8 +9964,12 @@
       <c r="X251" s="3"/>
       <c r="Y251" s="3"/>
       <c r="Z251" s="3"/>
-    </row>
-    <row r="252" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA251" s="3"/>
+      <c r="AB251" s="3"/>
+      <c r="AC251" s="3"/>
+      <c r="AD251" s="3"/>
+    </row>
+    <row r="252" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -8855,8 +9994,12 @@
       <c r="X252" s="3"/>
       <c r="Y252" s="3"/>
       <c r="Z252" s="3"/>
-    </row>
-    <row r="253" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA252" s="3"/>
+      <c r="AB252" s="3"/>
+      <c r="AC252" s="3"/>
+      <c r="AD252" s="3"/>
+    </row>
+    <row r="253" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -8881,8 +10024,12 @@
       <c r="X253" s="3"/>
       <c r="Y253" s="3"/>
       <c r="Z253" s="3"/>
-    </row>
-    <row r="254" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA253" s="3"/>
+      <c r="AB253" s="3"/>
+      <c r="AC253" s="3"/>
+      <c r="AD253" s="3"/>
+    </row>
+    <row r="254" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -8907,8 +10054,12 @@
       <c r="X254" s="3"/>
       <c r="Y254" s="3"/>
       <c r="Z254" s="3"/>
-    </row>
-    <row r="255" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA254" s="3"/>
+      <c r="AB254" s="3"/>
+      <c r="AC254" s="3"/>
+      <c r="AD254" s="3"/>
+    </row>
+    <row r="255" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -8933,8 +10084,12 @@
       <c r="X255" s="3"/>
       <c r="Y255" s="3"/>
       <c r="Z255" s="3"/>
-    </row>
-    <row r="256" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA255" s="3"/>
+      <c r="AB255" s="3"/>
+      <c r="AC255" s="3"/>
+      <c r="AD255" s="3"/>
+    </row>
+    <row r="256" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -8959,8 +10114,12 @@
       <c r="X256" s="3"/>
       <c r="Y256" s="3"/>
       <c r="Z256" s="3"/>
-    </row>
-    <row r="257" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA256" s="3"/>
+      <c r="AB256" s="3"/>
+      <c r="AC256" s="3"/>
+      <c r="AD256" s="3"/>
+    </row>
+    <row r="257" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -8985,8 +10144,12 @@
       <c r="X257" s="3"/>
       <c r="Y257" s="3"/>
       <c r="Z257" s="3"/>
-    </row>
-    <row r="258" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA257" s="3"/>
+      <c r="AB257" s="3"/>
+      <c r="AC257" s="3"/>
+      <c r="AD257" s="3"/>
+    </row>
+    <row r="258" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -9011,8 +10174,12 @@
       <c r="X258" s="3"/>
       <c r="Y258" s="3"/>
       <c r="Z258" s="3"/>
-    </row>
-    <row r="259" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA258" s="3"/>
+      <c r="AB258" s="3"/>
+      <c r="AC258" s="3"/>
+      <c r="AD258" s="3"/>
+    </row>
+    <row r="259" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -9037,8 +10204,12 @@
       <c r="X259" s="3"/>
       <c r="Y259" s="3"/>
       <c r="Z259" s="3"/>
-    </row>
-    <row r="260" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA259" s="3"/>
+      <c r="AB259" s="3"/>
+      <c r="AC259" s="3"/>
+      <c r="AD259" s="3"/>
+    </row>
+    <row r="260" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -9063,8 +10234,12 @@
       <c r="X260" s="3"/>
       <c r="Y260" s="3"/>
       <c r="Z260" s="3"/>
-    </row>
-    <row r="261" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA260" s="3"/>
+      <c r="AB260" s="3"/>
+      <c r="AC260" s="3"/>
+      <c r="AD260" s="3"/>
+    </row>
+    <row r="261" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -9089,8 +10264,12 @@
       <c r="X261" s="3"/>
       <c r="Y261" s="3"/>
       <c r="Z261" s="3"/>
-    </row>
-    <row r="262" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA261" s="3"/>
+      <c r="AB261" s="3"/>
+      <c r="AC261" s="3"/>
+      <c r="AD261" s="3"/>
+    </row>
+    <row r="262" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -9115,8 +10294,12 @@
       <c r="X262" s="3"/>
       <c r="Y262" s="3"/>
       <c r="Z262" s="3"/>
-    </row>
-    <row r="263" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA262" s="3"/>
+      <c r="AB262" s="3"/>
+      <c r="AC262" s="3"/>
+      <c r="AD262" s="3"/>
+    </row>
+    <row r="263" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -9141,8 +10324,12 @@
       <c r="X263" s="3"/>
       <c r="Y263" s="3"/>
       <c r="Z263" s="3"/>
-    </row>
-    <row r="264" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA263" s="3"/>
+      <c r="AB263" s="3"/>
+      <c r="AC263" s="3"/>
+      <c r="AD263" s="3"/>
+    </row>
+    <row r="264" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -9167,8 +10354,12 @@
       <c r="X264" s="3"/>
       <c r="Y264" s="3"/>
       <c r="Z264" s="3"/>
-    </row>
-    <row r="265" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA264" s="3"/>
+      <c r="AB264" s="3"/>
+      <c r="AC264" s="3"/>
+      <c r="AD264" s="3"/>
+    </row>
+    <row r="265" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -9193,8 +10384,12 @@
       <c r="X265" s="3"/>
       <c r="Y265" s="3"/>
       <c r="Z265" s="3"/>
-    </row>
-    <row r="266" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA265" s="3"/>
+      <c r="AB265" s="3"/>
+      <c r="AC265" s="3"/>
+      <c r="AD265" s="3"/>
+    </row>
+    <row r="266" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -9219,8 +10414,12 @@
       <c r="X266" s="3"/>
       <c r="Y266" s="3"/>
       <c r="Z266" s="3"/>
-    </row>
-    <row r="267" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA266" s="3"/>
+      <c r="AB266" s="3"/>
+      <c r="AC266" s="3"/>
+      <c r="AD266" s="3"/>
+    </row>
+    <row r="267" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -9245,8 +10444,12 @@
       <c r="X267" s="3"/>
       <c r="Y267" s="3"/>
       <c r="Z267" s="3"/>
-    </row>
-    <row r="268" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA267" s="3"/>
+      <c r="AB267" s="3"/>
+      <c r="AC267" s="3"/>
+      <c r="AD267" s="3"/>
+    </row>
+    <row r="268" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -9271,8 +10474,12 @@
       <c r="X268" s="3"/>
       <c r="Y268" s="3"/>
       <c r="Z268" s="3"/>
-    </row>
-    <row r="269" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA268" s="3"/>
+      <c r="AB268" s="3"/>
+      <c r="AC268" s="3"/>
+      <c r="AD268" s="3"/>
+    </row>
+    <row r="269" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -9297,8 +10504,12 @@
       <c r="X269" s="3"/>
       <c r="Y269" s="3"/>
       <c r="Z269" s="3"/>
-    </row>
-    <row r="270" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA269" s="3"/>
+      <c r="AB269" s="3"/>
+      <c r="AC269" s="3"/>
+      <c r="AD269" s="3"/>
+    </row>
+    <row r="270" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -9323,8 +10534,12 @@
       <c r="X270" s="3"/>
       <c r="Y270" s="3"/>
       <c r="Z270" s="3"/>
-    </row>
-    <row r="271" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA270" s="3"/>
+      <c r="AB270" s="3"/>
+      <c r="AC270" s="3"/>
+      <c r="AD270" s="3"/>
+    </row>
+    <row r="271" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -9349,8 +10564,12 @@
       <c r="X271" s="3"/>
       <c r="Y271" s="3"/>
       <c r="Z271" s="3"/>
-    </row>
-    <row r="272" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA271" s="3"/>
+      <c r="AB271" s="3"/>
+      <c r="AC271" s="3"/>
+      <c r="AD271" s="3"/>
+    </row>
+    <row r="272" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -9375,8 +10594,12 @@
       <c r="X272" s="3"/>
       <c r="Y272" s="3"/>
       <c r="Z272" s="3"/>
-    </row>
-    <row r="273" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA272" s="3"/>
+      <c r="AB272" s="3"/>
+      <c r="AC272" s="3"/>
+      <c r="AD272" s="3"/>
+    </row>
+    <row r="273" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -9401,8 +10624,12 @@
       <c r="X273" s="3"/>
       <c r="Y273" s="3"/>
       <c r="Z273" s="3"/>
-    </row>
-    <row r="274" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA273" s="3"/>
+      <c r="AB273" s="3"/>
+      <c r="AC273" s="3"/>
+      <c r="AD273" s="3"/>
+    </row>
+    <row r="274" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -9427,8 +10654,12 @@
       <c r="X274" s="3"/>
       <c r="Y274" s="3"/>
       <c r="Z274" s="3"/>
-    </row>
-    <row r="275" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA274" s="3"/>
+      <c r="AB274" s="3"/>
+      <c r="AC274" s="3"/>
+      <c r="AD274" s="3"/>
+    </row>
+    <row r="275" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -9453,8 +10684,12 @@
       <c r="X275" s="3"/>
       <c r="Y275" s="3"/>
       <c r="Z275" s="3"/>
-    </row>
-    <row r="276" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA275" s="3"/>
+      <c r="AB275" s="3"/>
+      <c r="AC275" s="3"/>
+      <c r="AD275" s="3"/>
+    </row>
+    <row r="276" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -9479,8 +10714,12 @@
       <c r="X276" s="3"/>
       <c r="Y276" s="3"/>
       <c r="Z276" s="3"/>
-    </row>
-    <row r="277" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA276" s="3"/>
+      <c r="AB276" s="3"/>
+      <c r="AC276" s="3"/>
+      <c r="AD276" s="3"/>
+    </row>
+    <row r="277" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -9505,8 +10744,12 @@
       <c r="X277" s="3"/>
       <c r="Y277" s="3"/>
       <c r="Z277" s="3"/>
-    </row>
-    <row r="278" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA277" s="3"/>
+      <c r="AB277" s="3"/>
+      <c r="AC277" s="3"/>
+      <c r="AD277" s="3"/>
+    </row>
+    <row r="278" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -9531,8 +10774,12 @@
       <c r="X278" s="3"/>
       <c r="Y278" s="3"/>
       <c r="Z278" s="3"/>
-    </row>
-    <row r="279" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA278" s="3"/>
+      <c r="AB278" s="3"/>
+      <c r="AC278" s="3"/>
+      <c r="AD278" s="3"/>
+    </row>
+    <row r="279" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -9557,8 +10804,12 @@
       <c r="X279" s="3"/>
       <c r="Y279" s="3"/>
       <c r="Z279" s="3"/>
-    </row>
-    <row r="280" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA279" s="3"/>
+      <c r="AB279" s="3"/>
+      <c r="AC279" s="3"/>
+      <c r="AD279" s="3"/>
+    </row>
+    <row r="280" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -9583,8 +10834,12 @@
       <c r="X280" s="3"/>
       <c r="Y280" s="3"/>
       <c r="Z280" s="3"/>
-    </row>
-    <row r="281" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA280" s="3"/>
+      <c r="AB280" s="3"/>
+      <c r="AC280" s="3"/>
+      <c r="AD280" s="3"/>
+    </row>
+    <row r="281" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -9609,8 +10864,12 @@
       <c r="X281" s="3"/>
       <c r="Y281" s="3"/>
       <c r="Z281" s="3"/>
-    </row>
-    <row r="282" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA281" s="3"/>
+      <c r="AB281" s="3"/>
+      <c r="AC281" s="3"/>
+      <c r="AD281" s="3"/>
+    </row>
+    <row r="282" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -9635,8 +10894,12 @@
       <c r="X282" s="3"/>
       <c r="Y282" s="3"/>
       <c r="Z282" s="3"/>
-    </row>
-    <row r="283" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA282" s="3"/>
+      <c r="AB282" s="3"/>
+      <c r="AC282" s="3"/>
+      <c r="AD282" s="3"/>
+    </row>
+    <row r="283" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="3"/>
@@ -9661,8 +10924,12 @@
       <c r="X283" s="3"/>
       <c r="Y283" s="3"/>
       <c r="Z283" s="3"/>
-    </row>
-    <row r="284" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA283" s="3"/>
+      <c r="AB283" s="3"/>
+      <c r="AC283" s="3"/>
+      <c r="AD283" s="3"/>
+    </row>
+    <row r="284" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -9687,8 +10954,12 @@
       <c r="X284" s="3"/>
       <c r="Y284" s="3"/>
       <c r="Z284" s="3"/>
-    </row>
-    <row r="285" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA284" s="3"/>
+      <c r="AB284" s="3"/>
+      <c r="AC284" s="3"/>
+      <c r="AD284" s="3"/>
+    </row>
+    <row r="285" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
@@ -9713,8 +10984,12 @@
       <c r="X285" s="3"/>
       <c r="Y285" s="3"/>
       <c r="Z285" s="3"/>
-    </row>
-    <row r="286" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA285" s="3"/>
+      <c r="AB285" s="3"/>
+      <c r="AC285" s="3"/>
+      <c r="AD285" s="3"/>
+    </row>
+    <row r="286" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -9739,8 +11014,12 @@
       <c r="X286" s="3"/>
       <c r="Y286" s="3"/>
       <c r="Z286" s="3"/>
-    </row>
-    <row r="287" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA286" s="3"/>
+      <c r="AB286" s="3"/>
+      <c r="AC286" s="3"/>
+      <c r="AD286" s="3"/>
+    </row>
+    <row r="287" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
       <c r="E287" s="3"/>
@@ -9765,8 +11044,12 @@
       <c r="X287" s="3"/>
       <c r="Y287" s="3"/>
       <c r="Z287" s="3"/>
-    </row>
-    <row r="288" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA287" s="3"/>
+      <c r="AB287" s="3"/>
+      <c r="AC287" s="3"/>
+      <c r="AD287" s="3"/>
+    </row>
+    <row r="288" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -9791,8 +11074,12 @@
       <c r="X288" s="3"/>
       <c r="Y288" s="3"/>
       <c r="Z288" s="3"/>
-    </row>
-    <row r="289" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA288" s="3"/>
+      <c r="AB288" s="3"/>
+      <c r="AC288" s="3"/>
+      <c r="AD288" s="3"/>
+    </row>
+    <row r="289" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -9817,8 +11104,12 @@
       <c r="X289" s="3"/>
       <c r="Y289" s="3"/>
       <c r="Z289" s="3"/>
-    </row>
-    <row r="290" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA289" s="3"/>
+      <c r="AB289" s="3"/>
+      <c r="AC289" s="3"/>
+      <c r="AD289" s="3"/>
+    </row>
+    <row r="290" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -9843,8 +11134,12 @@
       <c r="X290" s="3"/>
       <c r="Y290" s="3"/>
       <c r="Z290" s="3"/>
-    </row>
-    <row r="291" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA290" s="3"/>
+      <c r="AB290" s="3"/>
+      <c r="AC290" s="3"/>
+      <c r="AD290" s="3"/>
+    </row>
+    <row r="291" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
@@ -9869,8 +11164,12 @@
       <c r="X291" s="3"/>
       <c r="Y291" s="3"/>
       <c r="Z291" s="3"/>
-    </row>
-    <row r="292" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA291" s="3"/>
+      <c r="AB291" s="3"/>
+      <c r="AC291" s="3"/>
+      <c r="AD291" s="3"/>
+    </row>
+    <row r="292" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -9895,8 +11194,12 @@
       <c r="X292" s="3"/>
       <c r="Y292" s="3"/>
       <c r="Z292" s="3"/>
-    </row>
-    <row r="293" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA292" s="3"/>
+      <c r="AB292" s="3"/>
+      <c r="AC292" s="3"/>
+      <c r="AD292" s="3"/>
+    </row>
+    <row r="293" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="3"/>
@@ -9921,8 +11224,12 @@
       <c r="X293" s="3"/>
       <c r="Y293" s="3"/>
       <c r="Z293" s="3"/>
-    </row>
-    <row r="294" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA293" s="3"/>
+      <c r="AB293" s="3"/>
+      <c r="AC293" s="3"/>
+      <c r="AD293" s="3"/>
+    </row>
+    <row r="294" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -9947,8 +11254,12 @@
       <c r="X294" s="3"/>
       <c r="Y294" s="3"/>
       <c r="Z294" s="3"/>
-    </row>
-    <row r="295" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA294" s="3"/>
+      <c r="AB294" s="3"/>
+      <c r="AC294" s="3"/>
+      <c r="AD294" s="3"/>
+    </row>
+    <row r="295" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
@@ -9973,8 +11284,12 @@
       <c r="X295" s="3"/>
       <c r="Y295" s="3"/>
       <c r="Z295" s="3"/>
-    </row>
-    <row r="296" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA295" s="3"/>
+      <c r="AB295" s="3"/>
+      <c r="AC295" s="3"/>
+      <c r="AD295" s="3"/>
+    </row>
+    <row r="296" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -9999,8 +11314,12 @@
       <c r="X296" s="3"/>
       <c r="Y296" s="3"/>
       <c r="Z296" s="3"/>
-    </row>
-    <row r="297" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA296" s="3"/>
+      <c r="AB296" s="3"/>
+      <c r="AC296" s="3"/>
+      <c r="AD296" s="3"/>
+    </row>
+    <row r="297" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="3"/>
@@ -10025,8 +11344,12 @@
       <c r="X297" s="3"/>
       <c r="Y297" s="3"/>
       <c r="Z297" s="3"/>
-    </row>
-    <row r="298" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA297" s="3"/>
+      <c r="AB297" s="3"/>
+      <c r="AC297" s="3"/>
+      <c r="AD297" s="3"/>
+    </row>
+    <row r="298" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -10051,8 +11374,12 @@
       <c r="X298" s="3"/>
       <c r="Y298" s="3"/>
       <c r="Z298" s="3"/>
-    </row>
-    <row r="299" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA298" s="3"/>
+      <c r="AB298" s="3"/>
+      <c r="AC298" s="3"/>
+      <c r="AD298" s="3"/>
+    </row>
+    <row r="299" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
       <c r="E299" s="3"/>
@@ -10077,8 +11404,12 @@
       <c r="X299" s="3"/>
       <c r="Y299" s="3"/>
       <c r="Z299" s="3"/>
-    </row>
-    <row r="300" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA299" s="3"/>
+      <c r="AB299" s="3"/>
+      <c r="AC299" s="3"/>
+      <c r="AD299" s="3"/>
+    </row>
+    <row r="300" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -10103,8 +11434,12 @@
       <c r="X300" s="3"/>
       <c r="Y300" s="3"/>
       <c r="Z300" s="3"/>
-    </row>
-    <row r="301" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA300" s="3"/>
+      <c r="AB300" s="3"/>
+      <c r="AC300" s="3"/>
+      <c r="AD300" s="3"/>
+    </row>
+    <row r="301" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
       <c r="E301" s="3"/>
@@ -10129,8 +11464,12 @@
       <c r="X301" s="3"/>
       <c r="Y301" s="3"/>
       <c r="Z301" s="3"/>
-    </row>
-    <row r="302" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA301" s="3"/>
+      <c r="AB301" s="3"/>
+      <c r="AC301" s="3"/>
+      <c r="AD301" s="3"/>
+    </row>
+    <row r="302" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
       <c r="E302" s="3"/>
@@ -10155,8 +11494,12 @@
       <c r="X302" s="3"/>
       <c r="Y302" s="3"/>
       <c r="Z302" s="3"/>
-    </row>
-    <row r="303" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA302" s="3"/>
+      <c r="AB302" s="3"/>
+      <c r="AC302" s="3"/>
+      <c r="AD302" s="3"/>
+    </row>
+    <row r="303" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
       <c r="E303" s="3"/>
@@ -10181,8 +11524,12 @@
       <c r="X303" s="3"/>
       <c r="Y303" s="3"/>
       <c r="Z303" s="3"/>
-    </row>
-    <row r="304" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA303" s="3"/>
+      <c r="AB303" s="3"/>
+      <c r="AC303" s="3"/>
+      <c r="AD303" s="3"/>
+    </row>
+    <row r="304" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
       <c r="E304" s="3"/>
@@ -10207,8 +11554,12 @@
       <c r="X304" s="3"/>
       <c r="Y304" s="3"/>
       <c r="Z304" s="3"/>
-    </row>
-    <row r="305" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA304" s="3"/>
+      <c r="AB304" s="3"/>
+      <c r="AC304" s="3"/>
+      <c r="AD304" s="3"/>
+    </row>
+    <row r="305" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="3"/>
@@ -10233,8 +11584,12 @@
       <c r="X305" s="3"/>
       <c r="Y305" s="3"/>
       <c r="Z305" s="3"/>
-    </row>
-    <row r="306" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA305" s="3"/>
+      <c r="AB305" s="3"/>
+      <c r="AC305" s="3"/>
+      <c r="AD305" s="3"/>
+    </row>
+    <row r="306" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
       <c r="E306" s="3"/>
@@ -10259,8 +11614,12 @@
       <c r="X306" s="3"/>
       <c r="Y306" s="3"/>
       <c r="Z306" s="3"/>
-    </row>
-    <row r="307" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA306" s="3"/>
+      <c r="AB306" s="3"/>
+      <c r="AC306" s="3"/>
+      <c r="AD306" s="3"/>
+    </row>
+    <row r="307" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
       <c r="E307" s="3"/>
@@ -10285,8 +11644,12 @@
       <c r="X307" s="3"/>
       <c r="Y307" s="3"/>
       <c r="Z307" s="3"/>
-    </row>
-    <row r="308" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA307" s="3"/>
+      <c r="AB307" s="3"/>
+      <c r="AC307" s="3"/>
+      <c r="AD307" s="3"/>
+    </row>
+    <row r="308" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
       <c r="E308" s="3"/>
@@ -10311,8 +11674,12 @@
       <c r="X308" s="3"/>
       <c r="Y308" s="3"/>
       <c r="Z308" s="3"/>
-    </row>
-    <row r="309" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA308" s="3"/>
+      <c r="AB308" s="3"/>
+      <c r="AC308" s="3"/>
+      <c r="AD308" s="3"/>
+    </row>
+    <row r="309" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
       <c r="E309" s="3"/>
@@ -10337,8 +11704,12 @@
       <c r="X309" s="3"/>
       <c r="Y309" s="3"/>
       <c r="Z309" s="3"/>
-    </row>
-    <row r="310" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA309" s="3"/>
+      <c r="AB309" s="3"/>
+      <c r="AC309" s="3"/>
+      <c r="AD309" s="3"/>
+    </row>
+    <row r="310" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
       <c r="E310" s="3"/>
@@ -10363,8 +11734,12 @@
       <c r="X310" s="3"/>
       <c r="Y310" s="3"/>
       <c r="Z310" s="3"/>
-    </row>
-    <row r="311" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA310" s="3"/>
+      <c r="AB310" s="3"/>
+      <c r="AC310" s="3"/>
+      <c r="AD310" s="3"/>
+    </row>
+    <row r="311" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
       <c r="E311" s="3"/>
@@ -10389,8 +11764,12 @@
       <c r="X311" s="3"/>
       <c r="Y311" s="3"/>
       <c r="Z311" s="3"/>
-    </row>
-    <row r="312" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA311" s="3"/>
+      <c r="AB311" s="3"/>
+      <c r="AC311" s="3"/>
+      <c r="AD311" s="3"/>
+    </row>
+    <row r="312" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
       <c r="E312" s="3"/>
@@ -10415,8 +11794,12 @@
       <c r="X312" s="3"/>
       <c r="Y312" s="3"/>
       <c r="Z312" s="3"/>
-    </row>
-    <row r="313" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA312" s="3"/>
+      <c r="AB312" s="3"/>
+      <c r="AC312" s="3"/>
+      <c r="AD312" s="3"/>
+    </row>
+    <row r="313" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
       <c r="E313" s="3"/>
@@ -10441,8 +11824,12 @@
       <c r="X313" s="3"/>
       <c r="Y313" s="3"/>
       <c r="Z313" s="3"/>
-    </row>
-    <row r="314" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA313" s="3"/>
+      <c r="AB313" s="3"/>
+      <c r="AC313" s="3"/>
+      <c r="AD313" s="3"/>
+    </row>
+    <row r="314" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
       <c r="E314" s="3"/>
@@ -10467,8 +11854,12 @@
       <c r="X314" s="3"/>
       <c r="Y314" s="3"/>
       <c r="Z314" s="3"/>
-    </row>
-    <row r="315" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA314" s="3"/>
+      <c r="AB314" s="3"/>
+      <c r="AC314" s="3"/>
+      <c r="AD314" s="3"/>
+    </row>
+    <row r="315" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
       <c r="E315" s="3"/>
@@ -10493,8 +11884,12 @@
       <c r="X315" s="3"/>
       <c r="Y315" s="3"/>
       <c r="Z315" s="3"/>
-    </row>
-    <row r="316" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA315" s="3"/>
+      <c r="AB315" s="3"/>
+      <c r="AC315" s="3"/>
+      <c r="AD315" s="3"/>
+    </row>
+    <row r="316" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
       <c r="E316" s="3"/>
@@ -10519,8 +11914,12 @@
       <c r="X316" s="3"/>
       <c r="Y316" s="3"/>
       <c r="Z316" s="3"/>
-    </row>
-    <row r="317" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA316" s="3"/>
+      <c r="AB316" s="3"/>
+      <c r="AC316" s="3"/>
+      <c r="AD316" s="3"/>
+    </row>
+    <row r="317" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
       <c r="E317" s="3"/>
@@ -10545,8 +11944,12 @@
       <c r="X317" s="3"/>
       <c r="Y317" s="3"/>
       <c r="Z317" s="3"/>
-    </row>
-    <row r="318" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA317" s="3"/>
+      <c r="AB317" s="3"/>
+      <c r="AC317" s="3"/>
+      <c r="AD317" s="3"/>
+    </row>
+    <row r="318" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
       <c r="E318" s="3"/>
@@ -10571,8 +11974,12 @@
       <c r="X318" s="3"/>
       <c r="Y318" s="3"/>
       <c r="Z318" s="3"/>
-    </row>
-    <row r="319" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA318" s="3"/>
+      <c r="AB318" s="3"/>
+      <c r="AC318" s="3"/>
+      <c r="AD318" s="3"/>
+    </row>
+    <row r="319" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
       <c r="E319" s="3"/>
@@ -10597,8 +12004,12 @@
       <c r="X319" s="3"/>
       <c r="Y319" s="3"/>
       <c r="Z319" s="3"/>
-    </row>
-    <row r="320" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA319" s="3"/>
+      <c r="AB319" s="3"/>
+      <c r="AC319" s="3"/>
+      <c r="AD319" s="3"/>
+    </row>
+    <row r="320" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
       <c r="E320" s="3"/>
@@ -10623,8 +12034,12 @@
       <c r="X320" s="3"/>
       <c r="Y320" s="3"/>
       <c r="Z320" s="3"/>
-    </row>
-    <row r="321" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA320" s="3"/>
+      <c r="AB320" s="3"/>
+      <c r="AC320" s="3"/>
+      <c r="AD320" s="3"/>
+    </row>
+    <row r="321" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
       <c r="E321" s="3"/>
@@ -10649,8 +12064,12 @@
       <c r="X321" s="3"/>
       <c r="Y321" s="3"/>
       <c r="Z321" s="3"/>
-    </row>
-    <row r="322" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA321" s="3"/>
+      <c r="AB321" s="3"/>
+      <c r="AC321" s="3"/>
+      <c r="AD321" s="3"/>
+    </row>
+    <row r="322" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
       <c r="E322" s="3"/>
@@ -10675,8 +12094,12 @@
       <c r="X322" s="3"/>
       <c r="Y322" s="3"/>
       <c r="Z322" s="3"/>
-    </row>
-    <row r="323" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA322" s="3"/>
+      <c r="AB322" s="3"/>
+      <c r="AC322" s="3"/>
+      <c r="AD322" s="3"/>
+    </row>
+    <row r="323" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
       <c r="E323" s="3"/>
@@ -10701,8 +12124,12 @@
       <c r="X323" s="3"/>
       <c r="Y323" s="3"/>
       <c r="Z323" s="3"/>
-    </row>
-    <row r="324" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA323" s="3"/>
+      <c r="AB323" s="3"/>
+      <c r="AC323" s="3"/>
+      <c r="AD323" s="3"/>
+    </row>
+    <row r="324" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
       <c r="E324" s="3"/>
@@ -10727,8 +12154,12 @@
       <c r="X324" s="3"/>
       <c r="Y324" s="3"/>
       <c r="Z324" s="3"/>
-    </row>
-    <row r="325" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA324" s="3"/>
+      <c r="AB324" s="3"/>
+      <c r="AC324" s="3"/>
+      <c r="AD324" s="3"/>
+    </row>
+    <row r="325" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C325" s="3"/>
       <c r="D325" s="3"/>
       <c r="E325" s="3"/>
@@ -10753,8 +12184,12 @@
       <c r="X325" s="3"/>
       <c r="Y325" s="3"/>
       <c r="Z325" s="3"/>
-    </row>
-    <row r="326" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA325" s="3"/>
+      <c r="AB325" s="3"/>
+      <c r="AC325" s="3"/>
+      <c r="AD325" s="3"/>
+    </row>
+    <row r="326" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C326" s="3"/>
       <c r="D326" s="3"/>
       <c r="E326" s="3"/>
@@ -10779,8 +12214,12 @@
       <c r="X326" s="3"/>
       <c r="Y326" s="3"/>
       <c r="Z326" s="3"/>
-    </row>
-    <row r="327" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA326" s="3"/>
+      <c r="AB326" s="3"/>
+      <c r="AC326" s="3"/>
+      <c r="AD326" s="3"/>
+    </row>
+    <row r="327" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C327" s="3"/>
       <c r="D327" s="3"/>
       <c r="E327" s="3"/>
@@ -10805,8 +12244,12 @@
       <c r="X327" s="3"/>
       <c r="Y327" s="3"/>
       <c r="Z327" s="3"/>
-    </row>
-    <row r="328" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA327" s="3"/>
+      <c r="AB327" s="3"/>
+      <c r="AC327" s="3"/>
+      <c r="AD327" s="3"/>
+    </row>
+    <row r="328" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C328" s="3"/>
       <c r="D328" s="3"/>
       <c r="E328" s="3"/>
@@ -10831,8 +12274,12 @@
       <c r="X328" s="3"/>
       <c r="Y328" s="3"/>
       <c r="Z328" s="3"/>
-    </row>
-    <row r="329" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA328" s="3"/>
+      <c r="AB328" s="3"/>
+      <c r="AC328" s="3"/>
+      <c r="AD328" s="3"/>
+    </row>
+    <row r="329" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C329" s="3"/>
       <c r="D329" s="3"/>
       <c r="E329" s="3"/>
@@ -10857,8 +12304,12 @@
       <c r="X329" s="3"/>
       <c r="Y329" s="3"/>
       <c r="Z329" s="3"/>
-    </row>
-    <row r="330" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA329" s="3"/>
+      <c r="AB329" s="3"/>
+      <c r="AC329" s="3"/>
+      <c r="AD329" s="3"/>
+    </row>
+    <row r="330" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
       <c r="E330" s="3"/>
@@ -10883,6 +12334,10 @@
       <c r="X330" s="3"/>
       <c r="Y330" s="3"/>
       <c r="Z330" s="3"/>
+      <c r="AA330" s="3"/>
+      <c r="AB330" s="3"/>
+      <c r="AC330" s="3"/>
+      <c r="AD330" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/LEVI.xlsx
+++ b/LEVI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39DC7321-BB3D-4D60-B837-A0828AA37A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E493B11-B6DC-4351-BBA9-EBE3D883BDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{D6D5C0B0-0DA9-4C26-A53F-ED546E3BB507}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{D6D5C0B0-0DA9-4C26-A53F-ED546E3BB507}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -890,7 +890,7 @@
         <v>3</v>
       </c>
       <c r="I2" s="3">
-        <v>22.76</v>
+        <v>22.68</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -915,7 +915,7 @@
       </c>
       <c r="I4" s="3">
         <f>I3*I2</f>
-        <v>8753.410672760001</v>
+        <v>8722.6429726799997</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -956,7 +956,7 @@
       </c>
       <c r="I7" s="3">
         <f>I4-I5+I6</f>
-        <v>8990.8106727600007</v>
+        <v>8960.0429726799994</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">

--- a/LEVI.xlsx
+++ b/LEVI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E493B11-B6DC-4351-BBA9-EBE3D883BDB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8689B5F1-0743-4DD0-AB69-8AEC96248096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" activeTab="1" xr2:uid="{D6D5C0B0-0DA9-4C26-A53F-ED546E3BB507}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{D6D5C0B0-0DA9-4C26-A53F-ED546E3BB507}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -278,13 +278,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -478,44 +484,48 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -890,7 +900,7 @@
         <v>3</v>
       </c>
       <c r="I2" s="3">
-        <v>22.68</v>
+        <v>24.26</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -898,11 +908,11 @@
         <v>4</v>
       </c>
       <c r="I3" s="3">
-        <f>98.176901+286.41935</f>
-        <v>384.596251</v>
-      </c>
-      <c r="J3" s="25" t="s">
-        <v>67</v>
+        <f>100.456337+248.394225</f>
+        <v>348.85056200000002</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -915,7 +925,7 @@
       </c>
       <c r="I4" s="3">
         <f>I3*I2</f>
-        <v>8722.6429726799997</v>
+        <v>8463.1146341200019</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -926,11 +936,11 @@
         <v>6</v>
       </c>
       <c r="I5" s="3">
-        <f>716.6+95.4</f>
-        <v>812</v>
-      </c>
-      <c r="J5" s="25" t="s">
-        <v>67</v>
+        <f>849.3+128.5</f>
+        <v>977.8</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -938,10 +948,10 @@
         <v>7</v>
       </c>
       <c r="I6" s="3">
-        <v>1049.4000000000001</v>
-      </c>
-      <c r="J6" s="25" t="s">
-        <v>67</v>
+        <v>1043</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -956,7 +966,7 @@
       </c>
       <c r="I7" s="3">
         <f>I4-I5+I6</f>
-        <v>8960.0429726799994</v>
+        <v>8528.3146341200008</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1132,7 +1142,9 @@
       <c r="O3" s="3">
         <v>855.7</v>
       </c>
-      <c r="P3" s="3"/>
+      <c r="P3" s="3">
+        <v>815.5</v>
+      </c>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -1189,7 +1201,9 @@
       <c r="O4" s="3">
         <v>496</v>
       </c>
-      <c r="P4" s="3"/>
+      <c r="P4" s="3">
+        <v>420.2</v>
+      </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
@@ -1246,7 +1260,9 @@
       <c r="O5" s="3">
         <v>347.5</v>
       </c>
-      <c r="P5" s="3"/>
+      <c r="P5" s="3">
+        <v>283.7</v>
+      </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
@@ -1303,7 +1319,9 @@
       <c r="O6" s="3">
         <v>831</v>
       </c>
-      <c r="P6" s="3"/>
+      <c r="P6" s="3">
+        <v>768.4</v>
+      </c>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
@@ -1360,7 +1378,9 @@
       <c r="O7" s="3">
         <v>911.5</v>
       </c>
-      <c r="P7" s="3"/>
+      <c r="P7" s="3">
+        <v>793.6</v>
+      </c>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
@@ -1419,7 +1439,9 @@
       <c r="O8" s="3">
         <v>1699.2</v>
       </c>
-      <c r="P8" s="3"/>
+      <c r="P8" s="3">
+        <v>1519.4</v>
+      </c>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
@@ -1476,7 +1498,9 @@
       <c r="O9" s="3">
         <v>43.3</v>
       </c>
-      <c r="P9" s="3"/>
+      <c r="P9" s="3">
+        <v>42.6</v>
+      </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
@@ -1547,7 +1571,9 @@
       <c r="O10" s="19">
         <v>1742.5</v>
       </c>
-      <c r="P10" s="19"/>
+      <c r="P10" s="19">
+        <v>1562</v>
+      </c>
       <c r="Q10" s="19"/>
       <c r="R10" s="19"/>
       <c r="S10" s="3"/>
@@ -1632,7 +1658,9 @@
       <c r="O11" s="24">
         <v>664.2</v>
       </c>
-      <c r="P11" s="24"/>
+      <c r="P11" s="24">
+        <v>582.9</v>
+      </c>
       <c r="Q11" s="24"/>
       <c r="R11" s="24"/>
       <c r="S11" s="3"/>
@@ -1727,7 +1755,10 @@
         <f>+O10-O11</f>
         <v>1078.3</v>
       </c>
-      <c r="P12" s="3"/>
+      <c r="P12" s="3">
+        <f>+P10-P11</f>
+        <v>979.1</v>
+      </c>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
@@ -1820,7 +1851,9 @@
       <c r="O13" s="24">
         <v>871.7</v>
       </c>
-      <c r="P13" s="24"/>
+      <c r="P13" s="27">
+        <v>843.4</v>
+      </c>
       <c r="Q13" s="24"/>
       <c r="R13" s="24"/>
       <c r="S13" s="3"/>
@@ -1907,7 +1940,9 @@
       <c r="O14" s="24">
         <v>7.9</v>
       </c>
-      <c r="P14" s="24"/>
+      <c r="P14" s="24">
+        <v>13.5</v>
+      </c>
       <c r="Q14" s="24"/>
       <c r="R14" s="24"/>
       <c r="S14" s="3"/>
@@ -1977,7 +2012,7 @@
         <v>20.899999999999977</v>
       </c>
       <c r="I15" s="3">
-        <f t="shared" ref="I15:O15" si="6">I12-SUM(I13:I14)</f>
+        <f t="shared" ref="I15:P15" si="6">I12-SUM(I13:I14)</f>
         <v>32.699999999999818</v>
       </c>
       <c r="J15" s="3">
@@ -2004,7 +2039,10 @@
         <f t="shared" si="6"/>
         <v>198.69999999999993</v>
       </c>
-      <c r="P15" s="3"/>
+      <c r="P15" s="3">
+        <f t="shared" si="6"/>
+        <v>122.20000000000005</v>
+      </c>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
@@ -2097,7 +2135,9 @@
       <c r="O16" s="24">
         <v>-13.1</v>
       </c>
-      <c r="P16" s="24"/>
+      <c r="P16" s="24">
+        <v>-12.9</v>
+      </c>
       <c r="Q16" s="24"/>
       <c r="R16" s="24"/>
       <c r="S16" s="3"/>
@@ -2182,7 +2222,9 @@
       <c r="O17" s="24">
         <v>42.6</v>
       </c>
-      <c r="P17" s="24"/>
+      <c r="P17" s="24">
+        <v>12.9</v>
+      </c>
       <c r="Q17" s="24"/>
       <c r="R17" s="24"/>
       <c r="S17" s="3"/>
@@ -2252,7 +2294,7 @@
         <v>10.999999999999977</v>
       </c>
       <c r="I18" s="3">
-        <f t="shared" ref="I18:O18" si="9">I15+I16+I17</f>
+        <f t="shared" ref="I18:P18" si="9">I15+I16+I17</f>
         <v>22.199999999999818</v>
       </c>
       <c r="J18" s="3">
@@ -2279,7 +2321,10 @@
         <f t="shared" si="9"/>
         <v>228.19999999999993</v>
       </c>
-      <c r="P18" s="3"/>
+      <c r="P18" s="3">
+        <f t="shared" si="9"/>
+        <v>122.20000000000005</v>
+      </c>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
@@ -2372,7 +2417,9 @@
       <c r="O19" s="24">
         <v>51.1</v>
       </c>
-      <c r="P19" s="24"/>
+      <c r="P19" s="24">
+        <v>27.4</v>
+      </c>
       <c r="Q19" s="24"/>
       <c r="R19" s="24"/>
       <c r="S19" s="3"/>
@@ -2448,7 +2495,9 @@
       <c r="O20" s="24">
         <v>1.3</v>
       </c>
-      <c r="P20" s="24"/>
+      <c r="P20" s="24">
+        <v>7.5</v>
+      </c>
       <c r="Q20" s="24"/>
       <c r="R20" s="24"/>
       <c r="S20" s="3"/>
@@ -2536,7 +2585,10 @@
         <f>+O18-O19-O20</f>
         <v>175.79999999999993</v>
       </c>
-      <c r="P21" s="3"/>
+      <c r="P21" s="3">
+        <f>+P18-P19-P20</f>
+        <v>87.30000000000004</v>
+      </c>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
@@ -2611,7 +2663,7 @@
         <v>36</v>
       </c>
       <c r="C23" s="20">
-        <f t="shared" ref="C23:O23" si="19">C21/C24</f>
+        <f t="shared" ref="C23:P23" si="19">C21/C24</f>
         <v>0.2896785180133899</v>
       </c>
       <c r="D23" s="20">
@@ -2662,7 +2714,10 @@
         <f t="shared" si="19"/>
         <v>0.45087586869263624</v>
       </c>
-      <c r="P23" s="20"/>
+      <c r="P23" s="20">
+        <f t="shared" si="19"/>
+        <v>0.22617632792539441</v>
+      </c>
       <c r="Q23" s="20"/>
       <c r="R23" s="20"/>
       <c r="S23" s="20"/>
@@ -2747,7 +2802,9 @@
       <c r="O24" s="3">
         <v>389.90776</v>
       </c>
-      <c r="P24" s="3"/>
+      <c r="P24" s="3">
+        <v>385.98203799999999</v>
+      </c>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
@@ -2839,7 +2896,7 @@
         <v>3.1482232130793264E-2</v>
       </c>
       <c r="L26" s="21">
-        <f t="shared" ref="L26:O28" si="26">L8/H8-1</f>
+        <f t="shared" ref="L26:P28" si="26">L8/H8-1</f>
         <v>6.2825250773059782E-2</v>
       </c>
       <c r="M26" s="21">
@@ -2847,14 +2904,17 @@
         <v>7.0522361613154727E-2</v>
       </c>
       <c r="N26" s="21" t="e">
-        <f t="shared" ref="N26:O27" si="28">N8/J8-1</f>
+        <f t="shared" ref="N26:P27" si="28">N8/J8-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="O26" s="21">
         <f t="shared" si="28"/>
         <v>0.11291590254126294</v>
       </c>
-      <c r="P26" s="21"/>
+      <c r="P26" s="21">
+        <f t="shared" si="28"/>
+        <v>7.8200397388589193E-2</v>
+      </c>
       <c r="Q26" s="21"/>
       <c r="R26" s="21"/>
       <c r="S26" s="3"/>
@@ -2915,7 +2975,10 @@
         <f t="shared" si="28"/>
         <v>0.23011363636363624</v>
       </c>
-      <c r="P27" s="21"/>
+      <c r="P27" s="21">
+        <f t="shared" si="28"/>
+        <v>0.15760869565217406</v>
+      </c>
       <c r="Q27" s="21"/>
       <c r="R27" s="21"/>
       <c r="S27" s="3"/>
@@ -2975,7 +3038,10 @@
         <f t="shared" si="26"/>
         <v>0.14127587110296047</v>
       </c>
-      <c r="P28" s="22"/>
+      <c r="P28" s="22">
+        <f t="shared" si="26"/>
+        <v>8.0221300138312523E-2</v>
+      </c>
       <c r="Q28" s="22"/>
       <c r="R28" s="22"/>
       <c r="S28" s="3"/>
@@ -3068,10 +3134,13 @@
         <v>0.60754332313965342</v>
       </c>
       <c r="O29" s="21">
-        <f t="shared" ref="O29" si="34">O12/O10</f>
+        <f t="shared" ref="O29:P29" si="34">O12/O10</f>
         <v>0.61882352941176466</v>
       </c>
-      <c r="P29" s="21"/>
+      <c r="P29" s="21">
+        <f t="shared" si="34"/>
+        <v>0.62682458386683737</v>
+      </c>
       <c r="Q29" s="21"/>
       <c r="R29" s="21"/>
       <c r="S29" s="3"/>
@@ -3164,10 +3233,13 @@
         <v>0.1192660550458715</v>
       </c>
       <c r="O30" s="21">
-        <f t="shared" ref="O30" si="40">O15/O10</f>
+        <f t="shared" ref="O30:P30" si="40">O15/O10</f>
         <v>0.11403156384505017</v>
       </c>
-      <c r="P30" s="21"/>
+      <c r="P30" s="21">
+        <f t="shared" si="40"/>
+        <v>7.8233034571062773E-2</v>
+      </c>
       <c r="Q30" s="21"/>
       <c r="R30" s="21"/>
       <c r="S30" s="3"/>
@@ -3260,10 +3332,13 @@
         <v>8.9477857061954824E-2</v>
       </c>
       <c r="O31" s="21">
-        <f t="shared" ref="O31" si="46">O21/O10</f>
+        <f t="shared" ref="O31:P31" si="46">O21/O10</f>
         <v>0.10088952654232421</v>
       </c>
-      <c r="P31" s="21"/>
+      <c r="P31" s="21">
+        <f t="shared" si="46"/>
+        <v>5.5889884763124224E-2</v>
+      </c>
       <c r="Q31" s="21"/>
       <c r="R31" s="21"/>
       <c r="S31" s="3"/>
@@ -3356,10 +3431,13 @@
         <v>0.19375943633618542</v>
       </c>
       <c r="O32" s="21">
-        <f t="shared" ref="O32" si="52">O19/O18</f>
+        <f t="shared" ref="O32:P32" si="52">O19/O18</f>
         <v>0.22392638036809823</v>
       </c>
-      <c r="P32" s="21"/>
+      <c r="P32" s="21">
+        <f t="shared" si="52"/>
+        <v>0.2242225859247135</v>
+      </c>
       <c r="Q32" s="21"/>
       <c r="R32" s="21"/>
       <c r="S32" s="3"/>
